--- a/3year_trades_report.xlsx
+++ b/3year_trades_report.xlsx
@@ -457,31 +457,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P93"/>
+  <dimension ref="A1:Q93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
+    <col width="97" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>INTRADAY TRADE LOG WITH EXACT ENTRY_TIME &amp; EXIT_TIME — NIFTY RELATIVE STRENGTH STRATEGY</t>
+          <t>INTRADAY TRADE LOG WITH SIGNAL TIME, ENTRY TIME &amp; EXIT TIME — NIFTY RELATIVE STRENGTH STRATEGY</t>
         </is>
       </c>
     </row>
@@ -506,70 +507,75 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Entry Time</t>
+          <t>Signal Trigger Time</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
+          <t>Entry Actual Time</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
           <t>Exit Time</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>Entry Price (Rs)</t>
         </is>
       </c>
-      <c r="H4" s="1" t="inlineStr">
+      <c r="I4" s="1" t="inlineStr">
         <is>
           <t>Exit Price (Rs)</t>
         </is>
       </c>
-      <c r="I4" s="1" t="inlineStr">
+      <c r="J4" s="1" t="inlineStr">
         <is>
           <t>Stop Loss (Rs)</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr">
+      <c r="K4" s="1" t="inlineStr">
         <is>
           <t>Target 1 (Rs)</t>
         </is>
       </c>
-      <c r="K4" s="1" t="inlineStr">
+      <c r="L4" s="1" t="inlineStr">
         <is>
           <t>Target 2 (Rs)</t>
         </is>
       </c>
-      <c r="L4" s="1" t="inlineStr">
+      <c r="M4" s="1" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="M4" s="1" t="inlineStr">
+      <c r="N4" s="1" t="inlineStr">
         <is>
           <t>Outcome</t>
         </is>
       </c>
-      <c r="N4" s="1" t="inlineStr">
+      <c r="O4" s="1" t="inlineStr">
         <is>
           <t>P&amp;L (Rs)</t>
         </is>
       </c>
-      <c r="O4" s="1" t="inlineStr">
+      <c r="P4" s="1" t="inlineStr">
         <is>
           <t>Return %</t>
         </is>
       </c>
-      <c r="P4" s="1" t="inlineStr">
+      <c r="Q4" s="1" t="inlineStr">
         <is>
           <t>Capital After (Rs)</t>
         </is>
@@ -586,54 +592,59 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>BDL</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="n">
         <v>1339.7</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="I5" s="3" t="n">
         <v>1366.49</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="J5" s="3" t="n">
         <v>1328.98</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="K5" s="3" t="n">
         <v>1355.78</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="L5" s="3" t="n">
         <v>1366.49</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="M5" s="2" t="n">
         <v>93</v>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="O5" s="3" t="n">
         <v>2491.84</v>
       </c>
-      <c r="O5" s="4" t="n">
+      <c r="P5" s="4" t="n">
         <v>0.024918</v>
       </c>
-      <c r="P5" s="3" t="n">
+      <c r="Q5" s="3" t="n">
         <v>102491.84</v>
       </c>
     </row>
@@ -648,54 +659,59 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>ACE</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>987.85</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="I6" s="3" t="n">
         <v>999.7</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="J6" s="3" t="n">
         <v>979.95</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="K6" s="3" t="n">
         <v>999.7</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="L6" s="3" t="n">
         <v>1007.61</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="M6" s="2" t="n">
         <v>129</v>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="O6" s="3" t="n">
         <v>1529.19</v>
       </c>
-      <c r="O6" s="4" t="n">
+      <c r="P6" s="4" t="n">
         <v>0.01492</v>
       </c>
-      <c r="P6" s="3" t="n">
+      <c r="Q6" s="3" t="n">
         <v>104021.03</v>
       </c>
     </row>
@@ -710,54 +726,59 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>APTUS</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="n">
         <v>268.95</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="I7" s="3" t="n">
         <v>272.18</v>
       </c>
-      <c r="I7" s="3" t="n">
+      <c r="J7" s="3" t="n">
         <v>266.8</v>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="K7" s="3" t="n">
         <v>272.18</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="L7" s="3" t="n">
         <v>274.33</v>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="M7" s="2" t="n">
         <v>483</v>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N7" s="3" t="n">
+      <c r="O7" s="3" t="n">
         <v>1558.83</v>
       </c>
-      <c r="O7" s="4" t="n">
+      <c r="P7" s="4" t="n">
         <v>0.014986</v>
       </c>
-      <c r="P7" s="3" t="n">
+      <c r="Q7" s="3" t="n">
         <v>105579.87</v>
       </c>
     </row>
@@ -772,54 +793,59 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>ABREL</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="n">
         <v>1330.8</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="I8" s="3" t="n">
         <v>1346.77</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="J8" s="3" t="n">
         <v>1320.15</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="K8" s="3" t="n">
         <v>1346.77</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="L8" s="3" t="n">
         <v>1357.42</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="M8" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N8" s="3" t="n">
+      <c r="O8" s="3" t="n">
         <v>1580.99</v>
       </c>
-      <c r="O8" s="4" t="n">
+      <c r="P8" s="4" t="n">
         <v>0.014974</v>
       </c>
-      <c r="P8" s="3" t="n">
+      <c r="Q8" s="3" t="n">
         <v>107160.86</v>
       </c>
     </row>
@@ -834,54 +860,59 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>09:15 AM</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>09:35 AM</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>BEML</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="n">
         <v>1770.2</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="I9" s="3" t="n">
         <v>1791.44</v>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="J9" s="3" t="n">
         <v>1756.04</v>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="K9" s="3" t="n">
         <v>1791.44</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="L9" s="3" t="n">
         <v>1805.6</v>
       </c>
-      <c r="L9" s="2" t="n">
+      <c r="M9" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N9" s="3" t="n">
+      <c r="O9" s="3" t="n">
         <v>1593.18</v>
       </c>
-      <c r="O9" s="4" t="n">
+      <c r="P9" s="4" t="n">
         <v>0.014867</v>
       </c>
-      <c r="P9" s="3" t="n">
+      <c r="Q9" s="3" t="n">
         <v>108754.04</v>
       </c>
     </row>
@@ -896,54 +927,59 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>ATHERENERG</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="n">
         <v>1140.6</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="I10" s="3" t="n">
         <v>1163.41</v>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="J10" s="3" t="n">
         <v>1131.48</v>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="K10" s="3" t="n">
         <v>1154.29</v>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="L10" s="3" t="n">
         <v>1163.41</v>
       </c>
-      <c r="L10" s="2" t="n">
+      <c r="M10" s="2" t="n">
         <v>119</v>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N10" s="3" t="n">
+      <c r="O10" s="3" t="n">
         <v>2714.63</v>
       </c>
-      <c r="O10" s="4" t="n">
+      <c r="P10" s="4" t="n">
         <v>0.024961</v>
       </c>
-      <c r="P10" s="3" t="n">
+      <c r="Q10" s="3" t="n">
         <v>111468.67</v>
       </c>
     </row>
@@ -958,54 +994,59 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>09:15 AM</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>09:25 AM</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>BPCL</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="n">
         <v>306.5</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="I11" s="3" t="n">
         <v>310.18</v>
       </c>
-      <c r="I11" s="3" t="n">
+      <c r="J11" s="3" t="n">
         <v>304.05</v>
       </c>
-      <c r="J11" s="3" t="n">
+      <c r="K11" s="3" t="n">
         <v>310.18</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="L11" s="3" t="n">
         <v>312.63</v>
       </c>
-      <c r="L11" s="2" t="n">
+      <c r="M11" s="2" t="n">
         <v>454</v>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N11" s="3" t="n">
+      <c r="O11" s="3" t="n">
         <v>1669.81</v>
       </c>
-      <c r="O11" s="4" t="n">
+      <c r="P11" s="4" t="n">
         <v>0.01498</v>
       </c>
-      <c r="P11" s="3" t="n">
+      <c r="Q11" s="3" t="n">
         <v>113138.48</v>
       </c>
     </row>
@@ -1020,54 +1061,59 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>09:15 AM</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>09:30 AM</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>ABFRL</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="n">
         <v>58.97</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="I12" s="3" t="n">
         <v>60.15</v>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="J12" s="3" t="n">
         <v>58.5</v>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="K12" s="3" t="n">
         <v>59.68</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="L12" s="3" t="n">
         <v>60.15</v>
       </c>
-      <c r="L12" s="2" t="n">
+      <c r="M12" s="2" t="n">
         <v>2398</v>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N12" s="3" t="n">
+      <c r="O12" s="3" t="n">
         <v>2828.2</v>
       </c>
-      <c r="O12" s="4" t="n">
+      <c r="P12" s="4" t="n">
         <v>0.024998</v>
       </c>
-      <c r="P12" s="3" t="n">
+      <c r="Q12" s="3" t="n">
         <v>115966.68</v>
       </c>
     </row>
@@ -1082,54 +1128,59 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>AARTIIND</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="n">
         <v>469</v>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="I13" s="3" t="n">
         <v>474.63</v>
       </c>
-      <c r="I13" s="3" t="n">
+      <c r="J13" s="3" t="n">
         <v>465.25</v>
       </c>
-      <c r="J13" s="3" t="n">
+      <c r="K13" s="3" t="n">
         <v>474.63</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="L13" s="3" t="n">
         <v>478.38</v>
       </c>
-      <c r="L13" s="2" t="n">
+      <c r="M13" s="2" t="n">
         <v>309</v>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N13" s="3" t="n">
+      <c r="O13" s="3" t="n">
         <v>1739.05</v>
       </c>
-      <c r="O13" s="4" t="n">
+      <c r="P13" s="4" t="n">
         <v>0.014996</v>
       </c>
-      <c r="P13" s="3" t="n">
+      <c r="Q13" s="3" t="n">
         <v>117705.73</v>
       </c>
     </row>
@@ -1144,54 +1195,59 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>AEGISVOPAK</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="n">
         <v>236.98</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="I14" s="3" t="n">
         <v>241.72</v>
       </c>
-      <c r="I14" s="3" t="n">
+      <c r="J14" s="3" t="n">
         <v>235.08</v>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="K14" s="3" t="n">
         <v>239.82</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="L14" s="3" t="n">
         <v>241.72</v>
       </c>
-      <c r="L14" s="2" t="n">
+      <c r="M14" s="2" t="n">
         <v>620</v>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N14" s="3" t="n">
+      <c r="O14" s="3" t="n">
         <v>2938.55</v>
       </c>
-      <c r="O14" s="4" t="n">
+      <c r="P14" s="4" t="n">
         <v>0.024965</v>
       </c>
-      <c r="P14" s="3" t="n">
+      <c r="Q14" s="3" t="n">
         <v>120644.28</v>
       </c>
     </row>
@@ -1206,54 +1262,59 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
+          <t>09:15 AM</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
           <t>09:25 AM</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>CPPLUS</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>3499</v>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
       </c>
       <c r="H15" s="6" t="n">
         <v>3499</v>
       </c>
       <c r="I15" s="6" t="n">
+        <v>3499</v>
+      </c>
+      <c r="J15" s="6" t="n">
         <v>3471.01</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="6" t="n">
         <v>3540.99</v>
       </c>
-      <c r="K15" s="6" t="n">
+      <c r="L15" s="6" t="n">
         <v>3568.98</v>
       </c>
-      <c r="L15" s="5" t="n">
+      <c r="M15" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="M15" s="5" t="inlineStr">
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>HIT_BE</t>
         </is>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="O15" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O15" s="7" t="n">
+      <c r="P15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="Q15" s="6" t="n">
         <v>120644.28</v>
       </c>
     </row>
@@ -1268,54 +1329,59 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>09:15 AM</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>09:30 AM</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>AUROPHARMA</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="n">
         <v>1568.9</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="I16" s="3" t="n">
         <v>1587.73</v>
       </c>
-      <c r="I16" s="3" t="n">
+      <c r="J16" s="3" t="n">
         <v>1556.35</v>
       </c>
-      <c r="J16" s="3" t="n">
+      <c r="K16" s="3" t="n">
         <v>1587.73</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="L16" s="3" t="n">
         <v>1600.28</v>
       </c>
-      <c r="L16" s="2" t="n">
+      <c r="M16" s="2" t="n">
         <v>96</v>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N16" s="3" t="n">
+      <c r="O16" s="3" t="n">
         <v>1807.37</v>
       </c>
-      <c r="O16" s="4" t="n">
+      <c r="P16" s="4" t="n">
         <v>0.014981</v>
       </c>
-      <c r="P16" s="3" t="n">
+      <c r="Q16" s="3" t="n">
         <v>122451.66</v>
       </c>
     </row>
@@ -1330,54 +1396,59 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>APARINDS</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="n">
         <v>14150</v>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="I17" s="3" t="n">
         <v>14433</v>
       </c>
-      <c r="I17" s="3" t="n">
+      <c r="J17" s="3" t="n">
         <v>14036.8</v>
       </c>
-      <c r="J17" s="3" t="n">
+      <c r="K17" s="3" t="n">
         <v>14319.8</v>
       </c>
-      <c r="K17" s="3" t="n">
+      <c r="L17" s="3" t="n">
         <v>14433</v>
       </c>
-      <c r="L17" s="2" t="n">
+      <c r="M17" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N17" s="3" t="n">
+      <c r="O17" s="3" t="n">
         <v>2830</v>
       </c>
-      <c r="O17" s="4" t="n">
+      <c r="P17" s="4" t="n">
         <v>0.023111</v>
       </c>
-      <c r="P17" s="3" t="n">
+      <c r="Q17" s="3" t="n">
         <v>125281.66</v>
       </c>
     </row>
@@ -1392,54 +1463,59 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
+          <t>09:15 AM</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
           <t>09:25 AM</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>AEGISLOG</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>1314.1</v>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
       </c>
       <c r="H18" s="6" t="n">
         <v>1314.1</v>
       </c>
       <c r="I18" s="6" t="n">
+        <v>1314.1</v>
+      </c>
+      <c r="J18" s="6" t="n">
         <v>1303.59</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="6" t="n">
         <v>1329.87</v>
       </c>
-      <c r="K18" s="6" t="n">
+      <c r="L18" s="6" t="n">
         <v>1340.38</v>
       </c>
-      <c r="L18" s="5" t="n">
+      <c r="M18" s="5" t="n">
         <v>119</v>
       </c>
-      <c r="M18" s="5" t="inlineStr">
+      <c r="N18" s="5" t="inlineStr">
         <is>
           <t>HIT_BE</t>
         </is>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="O18" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="7" t="n">
+      <c r="P18" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="Q18" s="6" t="n">
         <v>125281.66</v>
       </c>
     </row>
@@ -1454,54 +1530,59 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>BANDHANBNK</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="n">
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>200.96</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="I19" s="3" t="n">
         <v>204.98</v>
       </c>
-      <c r="I19" s="3" t="n">
+      <c r="J19" s="3" t="n">
         <v>199.35</v>
       </c>
-      <c r="J19" s="3" t="n">
+      <c r="K19" s="3" t="n">
         <v>203.37</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="L19" s="3" t="n">
         <v>204.98</v>
       </c>
-      <c r="L19" s="2" t="n">
+      <c r="M19" s="2" t="n">
         <v>779</v>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N19" s="3" t="n">
+      <c r="O19" s="3" t="n">
         <v>3130.96</v>
       </c>
-      <c r="O19" s="4" t="n">
+      <c r="P19" s="4" t="n">
         <v>0.024991</v>
       </c>
-      <c r="P19" s="3" t="n">
+      <c r="Q19" s="3" t="n">
         <v>128412.61</v>
       </c>
     </row>
@@ -1516,54 +1597,59 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>BELRISE</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="n">
         <v>223.7</v>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="I20" s="3" t="n">
         <v>226.38</v>
       </c>
-      <c r="I20" s="3" t="n">
+      <c r="J20" s="3" t="n">
         <v>221.91</v>
       </c>
-      <c r="J20" s="3" t="n">
+      <c r="K20" s="3" t="n">
         <v>226.38</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="L20" s="3" t="n">
         <v>228.17</v>
       </c>
-      <c r="L20" s="2" t="n">
+      <c r="M20" s="2" t="n">
         <v>717</v>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N20" s="3" t="n">
+      <c r="O20" s="3" t="n">
         <v>1924.71</v>
       </c>
-      <c r="O20" s="4" t="n">
+      <c r="P20" s="4" t="n">
         <v>0.014989</v>
       </c>
-      <c r="P20" s="3" t="n">
+      <c r="Q20" s="3" t="n">
         <v>130337.33</v>
       </c>
     </row>
@@ -1578,54 +1664,59 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>09:15 AM</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>09:45 AM</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>CPPLUS</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="n">
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="n">
         <v>3580</v>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="I21" s="3" t="n">
         <v>3622.96</v>
       </c>
-      <c r="I21" s="3" t="n">
+      <c r="J21" s="3" t="n">
         <v>3551.36</v>
       </c>
-      <c r="J21" s="3" t="n">
+      <c r="K21" s="3" t="n">
         <v>3622.96</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="L21" s="3" t="n">
         <v>3651.6</v>
       </c>
-      <c r="L21" s="2" t="n">
+      <c r="M21" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N21" s="3" t="n">
+      <c r="O21" s="3" t="n">
         <v>1933.2</v>
       </c>
-      <c r="O21" s="4" t="n">
+      <c r="P21" s="4" t="n">
         <v>0.014832</v>
       </c>
-      <c r="P21" s="3" t="n">
+      <c r="Q21" s="3" t="n">
         <v>132270.53</v>
       </c>
     </row>
@@ -1640,54 +1731,59 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>ALKEM</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="n">
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="n">
         <v>5635</v>
       </c>
-      <c r="H22" s="3" t="n">
+      <c r="I22" s="3" t="n">
         <v>5702.62</v>
       </c>
-      <c r="I22" s="3" t="n">
+      <c r="J22" s="3" t="n">
         <v>5589.92</v>
       </c>
-      <c r="J22" s="3" t="n">
+      <c r="K22" s="3" t="n">
         <v>5702.62</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="L22" s="3" t="n">
         <v>5747.7</v>
       </c>
-      <c r="L22" s="2" t="n">
+      <c r="M22" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N22" s="3" t="n">
+      <c r="O22" s="3" t="n">
         <v>1960.98</v>
       </c>
-      <c r="O22" s="4" t="n">
+      <c r="P22" s="4" t="n">
         <v>0.014826</v>
       </c>
-      <c r="P22" s="3" t="n">
+      <c r="Q22" s="3" t="n">
         <v>134231.51</v>
       </c>
     </row>
@@ -1702,54 +1798,59 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>ANTHEM</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="n">
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="n">
         <v>756.05</v>
       </c>
-      <c r="H23" s="3" t="n">
+      <c r="I23" s="3" t="n">
         <v>771.17</v>
       </c>
-      <c r="I23" s="3" t="n">
+      <c r="J23" s="3" t="n">
         <v>750</v>
       </c>
-      <c r="J23" s="3" t="n">
+      <c r="K23" s="3" t="n">
         <v>765.12</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="L23" s="3" t="n">
         <v>771.17</v>
       </c>
-      <c r="L23" s="2" t="n">
+      <c r="M23" s="2" t="n">
         <v>221</v>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N23" s="3" t="n">
+      <c r="O23" s="3" t="n">
         <v>3341.74</v>
       </c>
-      <c r="O23" s="4" t="n">
+      <c r="P23" s="4" t="n">
         <v>0.024895</v>
       </c>
-      <c r="P23" s="3" t="n">
+      <c r="Q23" s="3" t="n">
         <v>137573.25</v>
       </c>
     </row>
@@ -1764,54 +1865,59 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>ATHERENERG</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="n">
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="n">
         <v>1141.1</v>
       </c>
-      <c r="H24" s="3" t="n">
+      <c r="I24" s="3" t="n">
         <v>1154.79</v>
       </c>
-      <c r="I24" s="3" t="n">
+      <c r="J24" s="3" t="n">
         <v>1131.97</v>
       </c>
-      <c r="J24" s="3" t="n">
+      <c r="K24" s="3" t="n">
         <v>1154.79</v>
       </c>
-      <c r="K24" s="3" t="n">
+      <c r="L24" s="3" t="n">
         <v>1163.92</v>
       </c>
-      <c r="L24" s="2" t="n">
+      <c r="M24" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N24" s="3" t="n">
+      <c r="O24" s="3" t="n">
         <v>2053.98</v>
       </c>
-      <c r="O24" s="4" t="n">
+      <c r="P24" s="4" t="n">
         <v>0.01493</v>
       </c>
-      <c r="P24" s="3" t="n">
+      <c r="Q24" s="3" t="n">
         <v>139627.23</v>
       </c>
     </row>
@@ -1826,54 +1932,59 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>ADANIENSOL</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="n">
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="n">
         <v>1637.2</v>
       </c>
-      <c r="H25" s="3" t="n">
+      <c r="I25" s="3" t="n">
         <v>1656.85</v>
       </c>
-      <c r="I25" s="3" t="n">
+      <c r="J25" s="3" t="n">
         <v>1624.1</v>
       </c>
-      <c r="J25" s="3" t="n">
+      <c r="K25" s="3" t="n">
         <v>1656.85</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="L25" s="3" t="n">
         <v>1669.94</v>
       </c>
-      <c r="L25" s="2" t="n">
+      <c r="M25" s="2" t="n">
         <v>106</v>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N25" s="3" t="n">
+      <c r="O25" s="3" t="n">
         <v>2082.52</v>
       </c>
-      <c r="O25" s="4" t="n">
+      <c r="P25" s="4" t="n">
         <v>0.014915</v>
       </c>
-      <c r="P25" s="3" t="n">
+      <c r="Q25" s="3" t="n">
         <v>141709.75</v>
       </c>
     </row>
@@ -1888,54 +1999,59 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>CPPLUS</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="n">
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="n">
         <v>3554</v>
       </c>
-      <c r="H26" s="3" t="n">
+      <c r="I26" s="3" t="n">
         <v>3596.65</v>
       </c>
-      <c r="I26" s="3" t="n">
+      <c r="J26" s="3" t="n">
         <v>3525.57</v>
       </c>
-      <c r="J26" s="3" t="n">
+      <c r="K26" s="3" t="n">
         <v>3596.65</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="L26" s="3" t="n">
         <v>3625.08</v>
       </c>
-      <c r="L26" s="2" t="n">
+      <c r="M26" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N26" s="3" t="n">
+      <c r="O26" s="3" t="n">
         <v>2089.75</v>
       </c>
-      <c r="O26" s="4" t="n">
+      <c r="P26" s="4" t="n">
         <v>0.014747</v>
       </c>
-      <c r="P26" s="3" t="n">
+      <c r="Q26" s="3" t="n">
         <v>143799.5</v>
       </c>
     </row>
@@ -1950,54 +2066,59 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>BALRAMCHIN</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="n">
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="n">
         <v>558.85</v>
       </c>
-      <c r="H27" s="3" t="n">
+      <c r="I27" s="3" t="n">
         <v>570.03</v>
       </c>
-      <c r="I27" s="3" t="n">
+      <c r="J27" s="3" t="n">
         <v>554.38</v>
       </c>
-      <c r="J27" s="3" t="n">
+      <c r="K27" s="3" t="n">
         <v>565.5599999999999</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="L27" s="3" t="n">
         <v>570.03</v>
       </c>
-      <c r="L27" s="2" t="n">
+      <c r="M27" s="2" t="n">
         <v>321</v>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N27" s="3" t="n">
+      <c r="O27" s="3" t="n">
         <v>3587.82</v>
       </c>
-      <c r="O27" s="4" t="n">
+      <c r="P27" s="4" t="n">
         <v>0.02495</v>
       </c>
-      <c r="P27" s="3" t="n">
+      <c r="Q27" s="3" t="n">
         <v>147387.32</v>
       </c>
     </row>
@@ -2012,54 +2133,59 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>APARINDS</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="n">
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="n">
         <v>13471</v>
       </c>
-      <c r="H28" s="3" t="n">
+      <c r="I28" s="3" t="n">
         <v>13740.42</v>
       </c>
-      <c r="I28" s="3" t="n">
+      <c r="J28" s="3" t="n">
         <v>13363.23</v>
       </c>
-      <c r="J28" s="3" t="n">
+      <c r="K28" s="3" t="n">
         <v>13632.65</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="L28" s="3" t="n">
         <v>13740.42</v>
       </c>
-      <c r="L28" s="2" t="n">
+      <c r="M28" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N28" s="3" t="n">
+      <c r="O28" s="3" t="n">
         <v>3502.46</v>
       </c>
-      <c r="O28" s="4" t="n">
+      <c r="P28" s="4" t="n">
         <v>0.023764</v>
       </c>
-      <c r="P28" s="3" t="n">
+      <c r="Q28" s="3" t="n">
         <v>150889.78</v>
       </c>
     </row>
@@ -2074,54 +2200,59 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>BANDHANBNK</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="n">
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="n">
         <v>201.37</v>
       </c>
-      <c r="H29" s="3" t="n">
+      <c r="I29" s="3" t="n">
         <v>203.79</v>
       </c>
-      <c r="I29" s="3" t="n">
+      <c r="J29" s="3" t="n">
         <v>199.76</v>
       </c>
-      <c r="J29" s="3" t="n">
+      <c r="K29" s="3" t="n">
         <v>203.79</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="L29" s="3" t="n">
         <v>205.4</v>
       </c>
-      <c r="L29" s="2" t="n">
+      <c r="M29" s="2" t="n">
         <v>936</v>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N29" s="3" t="n">
+      <c r="O29" s="3" t="n">
         <v>2261.79</v>
       </c>
-      <c r="O29" s="4" t="n">
+      <c r="P29" s="4" t="n">
         <v>0.01499</v>
       </c>
-      <c r="P29" s="3" t="n">
+      <c r="Q29" s="3" t="n">
         <v>153151.56</v>
       </c>
     </row>
@@ -2136,54 +2267,59 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>09:15 AM</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>09:35 AM</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>ATGL</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="n">
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="n">
         <v>708</v>
       </c>
-      <c r="H30" s="3" t="n">
+      <c r="I30" s="3" t="n">
         <v>716.5</v>
       </c>
-      <c r="I30" s="3" t="n">
+      <c r="J30" s="3" t="n">
         <v>702.34</v>
       </c>
-      <c r="J30" s="3" t="n">
+      <c r="K30" s="3" t="n">
         <v>716.5</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="L30" s="3" t="n">
         <v>722.16</v>
       </c>
-      <c r="L30" s="2" t="n">
+      <c r="M30" s="2" t="n">
         <v>270</v>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N30" s="3" t="n">
+      <c r="O30" s="3" t="n">
         <v>2293.92</v>
       </c>
-      <c r="O30" s="4" t="n">
+      <c r="P30" s="4" t="n">
         <v>0.014978</v>
       </c>
-      <c r="P30" s="3" t="n">
+      <c r="Q30" s="3" t="n">
         <v>155445.48</v>
       </c>
     </row>
@@ -2198,54 +2334,59 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>AARTIIND</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="n">
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="n">
         <v>470.05</v>
       </c>
-      <c r="H31" s="3" t="n">
+      <c r="I31" s="3" t="n">
         <v>475.69</v>
       </c>
-      <c r="I31" s="3" t="n">
+      <c r="J31" s="3" t="n">
         <v>466.29</v>
       </c>
-      <c r="J31" s="3" t="n">
+      <c r="K31" s="3" t="n">
         <v>475.69</v>
       </c>
-      <c r="K31" s="3" t="n">
+      <c r="L31" s="3" t="n">
         <v>479.45</v>
       </c>
-      <c r="L31" s="2" t="n">
+      <c r="M31" s="2" t="n">
         <v>413</v>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N31" s="3" t="n">
+      <c r="O31" s="3" t="n">
         <v>2329.57</v>
       </c>
-      <c r="O31" s="4" t="n">
+      <c r="P31" s="4" t="n">
         <v>0.014986</v>
       </c>
-      <c r="P31" s="3" t="n">
+      <c r="Q31" s="3" t="n">
         <v>157775.05</v>
       </c>
     </row>
@@ -2260,54 +2401,59 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>BAJAJHLDNG</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="n">
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="n">
         <v>10291</v>
       </c>
-      <c r="H32" s="3" t="n">
+      <c r="I32" s="3" t="n">
         <v>10496.82</v>
       </c>
-      <c r="I32" s="3" t="n">
+      <c r="J32" s="3" t="n">
         <v>10208.67</v>
       </c>
-      <c r="J32" s="3" t="n">
+      <c r="K32" s="3" t="n">
         <v>10414.49</v>
       </c>
-      <c r="K32" s="3" t="n">
+      <c r="L32" s="3" t="n">
         <v>10496.82</v>
       </c>
-      <c r="L32" s="2" t="n">
+      <c r="M32" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N32" s="3" t="n">
+      <c r="O32" s="3" t="n">
         <v>3910.58</v>
       </c>
-      <c r="O32" s="4" t="n">
+      <c r="P32" s="4" t="n">
         <v>0.024786</v>
       </c>
-      <c r="P32" s="3" t="n">
+      <c r="Q32" s="3" t="n">
         <v>161685.63</v>
       </c>
     </row>
@@ -2322,54 +2468,59 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>BALRAMCHIN</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="n">
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="n">
         <v>569.5</v>
       </c>
-      <c r="H33" s="3" t="n">
+      <c r="I33" s="3" t="n">
         <v>580.89</v>
       </c>
-      <c r="I33" s="3" t="n">
+      <c r="J33" s="3" t="n">
         <v>564.9400000000001</v>
       </c>
-      <c r="J33" s="3" t="n">
+      <c r="K33" s="3" t="n">
         <v>576.33</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="L33" s="3" t="n">
         <v>580.89</v>
       </c>
-      <c r="L33" s="2" t="n">
+      <c r="M33" s="2" t="n">
         <v>354</v>
       </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N33" s="3" t="n">
+      <c r="O33" s="3" t="n">
         <v>4032.06</v>
       </c>
-      <c r="O33" s="4" t="n">
+      <c r="P33" s="4" t="n">
         <v>0.024938</v>
       </c>
-      <c r="P33" s="3" t="n">
+      <c r="Q33" s="3" t="n">
         <v>165717.69</v>
       </c>
     </row>
@@ -2384,54 +2535,59 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>AFFLE</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="n">
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="n">
         <v>1469.9</v>
       </c>
-      <c r="H34" s="3" t="n">
+      <c r="I34" s="3" t="n">
         <v>1499.3</v>
       </c>
-      <c r="I34" s="3" t="n">
+      <c r="J34" s="3" t="n">
         <v>1458.14</v>
       </c>
-      <c r="J34" s="3" t="n">
+      <c r="K34" s="3" t="n">
         <v>1487.54</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="L34" s="3" t="n">
         <v>1499.3</v>
       </c>
-      <c r="L34" s="2" t="n">
+      <c r="M34" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N34" s="3" t="n">
+      <c r="O34" s="3" t="n">
         <v>4115.72</v>
       </c>
-      <c r="O34" s="4" t="n">
+      <c r="P34" s="4" t="n">
         <v>0.024836</v>
       </c>
-      <c r="P34" s="3" t="n">
+      <c r="Q34" s="3" t="n">
         <v>169833.41</v>
       </c>
     </row>
@@ -2446,54 +2602,59 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>ASTRAL</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="n">
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="n">
         <v>1332.1</v>
       </c>
-      <c r="H35" s="3" t="n">
+      <c r="I35" s="3" t="n">
         <v>1348.09</v>
       </c>
-      <c r="I35" s="3" t="n">
+      <c r="J35" s="3" t="n">
         <v>1321.44</v>
       </c>
-      <c r="J35" s="3" t="n">
+      <c r="K35" s="3" t="n">
         <v>1348.09</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="L35" s="3" t="n">
         <v>1358.74</v>
       </c>
-      <c r="L35" s="2" t="n">
+      <c r="M35" s="2" t="n">
         <v>159</v>
       </c>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N35" s="3" t="n">
+      <c r="O35" s="3" t="n">
         <v>2541.65</v>
       </c>
-      <c r="O35" s="4" t="n">
+      <c r="P35" s="4" t="n">
         <v>0.014966</v>
       </c>
-      <c r="P35" s="3" t="n">
+      <c r="Q35" s="3" t="n">
         <v>172375.06</v>
       </c>
     </row>
@@ -2508,54 +2669,59 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>ASIANPAINT</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="n">
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="n">
         <v>2588</v>
       </c>
-      <c r="H36" s="3" t="n">
+      <c r="I36" s="3" t="n">
         <v>2639.76</v>
       </c>
-      <c r="I36" s="3" t="n">
+      <c r="J36" s="3" t="n">
         <v>2567.3</v>
       </c>
-      <c r="J36" s="3" t="n">
+      <c r="K36" s="3" t="n">
         <v>2619.06</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="L36" s="3" t="n">
         <v>2639.76</v>
       </c>
-      <c r="L36" s="2" t="n">
+      <c r="M36" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N36" s="3" t="n">
+      <c r="O36" s="3" t="n">
         <v>4296.08</v>
       </c>
-      <c r="O36" s="4" t="n">
+      <c r="P36" s="4" t="n">
         <v>0.024923</v>
       </c>
-      <c r="P36" s="3" t="n">
+      <c r="Q36" s="3" t="n">
         <v>176671.14</v>
       </c>
     </row>
@@ -2570,54 +2736,59 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>ANURAS</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="n">
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="n">
         <v>1261</v>
       </c>
-      <c r="H37" s="3" t="n">
+      <c r="I37" s="3" t="n">
         <v>1276.13</v>
       </c>
-      <c r="I37" s="3" t="n">
+      <c r="J37" s="3" t="n">
         <v>1250.91</v>
       </c>
-      <c r="J37" s="3" t="n">
+      <c r="K37" s="3" t="n">
         <v>1276.13</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="L37" s="3" t="n">
         <v>1286.22</v>
       </c>
-      <c r="L37" s="2" t="n">
+      <c r="M37" s="2" t="n">
         <v>175</v>
       </c>
-      <c r="M37" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N37" s="3" t="n">
+      <c r="O37" s="3" t="n">
         <v>2648.1</v>
       </c>
-      <c r="O37" s="4" t="n">
+      <c r="P37" s="4" t="n">
         <v>0.014989</v>
       </c>
-      <c r="P37" s="3" t="n">
+      <c r="Q37" s="3" t="n">
         <v>179319.24</v>
       </c>
     </row>
@@ -2632,54 +2803,59 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>ATHERENERG</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="n">
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="n">
         <v>1232.1</v>
       </c>
-      <c r="H38" s="3" t="n">
+      <c r="I38" s="3" t="n">
         <v>1256.74</v>
       </c>
-      <c r="I38" s="3" t="n">
+      <c r="J38" s="3" t="n">
         <v>1222.24</v>
       </c>
-      <c r="J38" s="3" t="n">
+      <c r="K38" s="3" t="n">
         <v>1246.89</v>
       </c>
-      <c r="K38" s="3" t="n">
+      <c r="L38" s="3" t="n">
         <v>1256.74</v>
       </c>
-      <c r="L38" s="2" t="n">
+      <c r="M38" s="2" t="n">
         <v>181</v>
       </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N38" s="3" t="n">
+      <c r="O38" s="3" t="n">
         <v>4460.2</v>
       </c>
-      <c r="O38" s="4" t="n">
+      <c r="P38" s="4" t="n">
         <v>0.024873</v>
       </c>
-      <c r="P38" s="3" t="n">
+      <c r="Q38" s="3" t="n">
         <v>183779.44</v>
       </c>
     </row>
@@ -2694,54 +2870,59 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>AEGISLOG</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="n">
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="n">
         <v>1235.5</v>
       </c>
-      <c r="H39" s="3" t="n">
+      <c r="I39" s="3" t="n">
         <v>1260.21</v>
       </c>
-      <c r="I39" s="3" t="n">
+      <c r="J39" s="3" t="n">
         <v>1225.62</v>
       </c>
-      <c r="J39" s="3" t="n">
+      <c r="K39" s="3" t="n">
         <v>1250.33</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="L39" s="3" t="n">
         <v>1260.21</v>
       </c>
-      <c r="L39" s="2" t="n">
+      <c r="M39" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="M39" s="2" t="inlineStr">
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N39" s="3" t="n">
+      <c r="O39" s="3" t="n">
         <v>4571.35</v>
       </c>
-      <c r="O39" s="4" t="n">
+      <c r="P39" s="4" t="n">
         <v>0.024874</v>
       </c>
-      <c r="P39" s="3" t="n">
+      <c r="Q39" s="3" t="n">
         <v>188350.79</v>
       </c>
     </row>
@@ -2756,54 +2937,59 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>BANDHANBNK</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="n">
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="n">
         <v>208.51</v>
       </c>
-      <c r="H40" s="3" t="n">
+      <c r="I40" s="3" t="n">
         <v>212.68</v>
       </c>
-      <c r="I40" s="3" t="n">
+      <c r="J40" s="3" t="n">
         <v>206.84</v>
       </c>
-      <c r="J40" s="3" t="n">
+      <c r="K40" s="3" t="n">
         <v>211.01</v>
       </c>
-      <c r="K40" s="3" t="n">
+      <c r="L40" s="3" t="n">
         <v>212.68</v>
       </c>
-      <c r="L40" s="2" t="n">
+      <c r="M40" s="2" t="n">
         <v>1129</v>
       </c>
-      <c r="M40" s="2" t="inlineStr">
+      <c r="N40" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N40" s="3" t="n">
+      <c r="O40" s="3" t="n">
         <v>4708.16</v>
       </c>
-      <c r="O40" s="4" t="n">
+      <c r="P40" s="4" t="n">
         <v>0.024997</v>
       </c>
-      <c r="P40" s="3" t="n">
+      <c r="Q40" s="3" t="n">
         <v>193058.95</v>
       </c>
     </row>
@@ -2818,54 +3004,59 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>CPPLUS</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="n">
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="n">
         <v>3749.3</v>
       </c>
-      <c r="H41" s="3" t="n">
+      <c r="I41" s="3" t="n">
         <v>3824.29</v>
       </c>
-      <c r="I41" s="3" t="n">
+      <c r="J41" s="3" t="n">
         <v>3719.31</v>
       </c>
-      <c r="J41" s="3" t="n">
+      <c r="K41" s="3" t="n">
         <v>3794.29</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="L41" s="3" t="n">
         <v>3824.29</v>
       </c>
-      <c r="L41" s="2" t="n">
+      <c r="M41" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="M41" s="2" t="inlineStr">
+      <c r="N41" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N41" s="3" t="n">
+      <c r="O41" s="3" t="n">
         <v>4799.1</v>
       </c>
-      <c r="O41" s="4" t="n">
+      <c r="P41" s="4" t="n">
         <v>0.024858</v>
       </c>
-      <c r="P41" s="3" t="n">
+      <c r="Q41" s="3" t="n">
         <v>197858.05</v>
       </c>
     </row>
@@ -2880,54 +3071,59 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>09:15 AM</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>09:35 AM</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>BPCL</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="n">
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="n">
         <v>311.5</v>
       </c>
-      <c r="H42" s="3" t="n">
+      <c r="I42" s="3" t="n">
         <v>315.24</v>
       </c>
-      <c r="I42" s="3" t="n">
+      <c r="J42" s="3" t="n">
         <v>309.01</v>
       </c>
-      <c r="J42" s="3" t="n">
+      <c r="K42" s="3" t="n">
         <v>315.24</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="L42" s="3" t="n">
         <v>317.73</v>
       </c>
-      <c r="L42" s="2" t="n">
+      <c r="M42" s="2" t="n">
         <v>793</v>
       </c>
-      <c r="M42" s="2" t="inlineStr">
+      <c r="N42" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N42" s="3" t="n">
+      <c r="O42" s="3" t="n">
         <v>2964.23</v>
       </c>
-      <c r="O42" s="4" t="n">
+      <c r="P42" s="4" t="n">
         <v>0.014982</v>
       </c>
-      <c r="P42" s="3" t="n">
+      <c r="Q42" s="3" t="n">
         <v>200822.28</v>
       </c>
     </row>
@@ -2942,54 +3138,59 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>3MINDIA</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="n">
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="n">
         <v>35940</v>
       </c>
-      <c r="H43" s="3" t="n">
+      <c r="I43" s="3" t="n">
         <v>36371.28</v>
       </c>
-      <c r="I43" s="3" t="n">
+      <c r="J43" s="3" t="n">
         <v>35652.48</v>
       </c>
-      <c r="J43" s="3" t="n">
+      <c r="K43" s="3" t="n">
         <v>36371.28</v>
       </c>
-      <c r="K43" s="3" t="n">
+      <c r="L43" s="3" t="n">
         <v>36658.8</v>
       </c>
-      <c r="L43" s="2" t="n">
+      <c r="M43" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="M43" s="2" t="inlineStr">
+      <c r="N43" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N43" s="3" t="n">
+      <c r="O43" s="3" t="n">
         <v>2587.68</v>
       </c>
-      <c r="O43" s="4" t="n">
+      <c r="P43" s="4" t="n">
         <v>0.012885</v>
       </c>
-      <c r="P43" s="3" t="n">
+      <c r="Q43" s="3" t="n">
         <v>203409.96</v>
       </c>
     </row>
@@ -3004,54 +3205,59 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>09:15 AM</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
           <t>09:35 AM</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>AFCONS</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="n">
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="n">
         <v>285</v>
       </c>
-      <c r="H44" s="3" t="n">
+      <c r="I44" s="3" t="n">
         <v>290.7</v>
       </c>
-      <c r="I44" s="3" t="n">
+      <c r="J44" s="3" t="n">
         <v>282.72</v>
       </c>
-      <c r="J44" s="3" t="n">
+      <c r="K44" s="3" t="n">
         <v>288.42</v>
       </c>
-      <c r="K44" s="3" t="n">
+      <c r="L44" s="3" t="n">
         <v>290.7</v>
       </c>
-      <c r="L44" s="2" t="n">
+      <c r="M44" s="2" t="n">
         <v>892</v>
       </c>
-      <c r="M44" s="2" t="inlineStr">
+      <c r="N44" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N44" s="3" t="n">
+      <c r="O44" s="3" t="n">
         <v>5084.4</v>
       </c>
-      <c r="O44" s="4" t="n">
+      <c r="P44" s="4" t="n">
         <v>0.024996</v>
       </c>
-      <c r="P44" s="3" t="n">
+      <c r="Q44" s="3" t="n">
         <v>208494.36</v>
       </c>
     </row>
@@ -3066,54 +3272,59 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
           <t>AEGISLOG</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G45" s="6" t="n">
-        <v>1309.8</v>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
       </c>
       <c r="H45" s="6" t="n">
         <v>1309.8</v>
       </c>
       <c r="I45" s="6" t="n">
+        <v>1309.8</v>
+      </c>
+      <c r="J45" s="6" t="n">
         <v>1299.32</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="K45" s="6" t="n">
         <v>1325.52</v>
       </c>
-      <c r="K45" s="6" t="n">
+      <c r="L45" s="6" t="n">
         <v>1336</v>
       </c>
-      <c r="L45" s="5" t="n">
+      <c r="M45" s="5" t="n">
         <v>198</v>
       </c>
-      <c r="M45" s="5" t="inlineStr">
+      <c r="N45" s="5" t="inlineStr">
         <is>
           <t>HIT_BE</t>
         </is>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="O45" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O45" s="7" t="n">
+      <c r="P45" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="Q45" s="6" t="n">
         <v>208494.36</v>
       </c>
     </row>
@@ -3128,54 +3339,59 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>09:15 AM</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
           <t>09:30 AM</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>ADANIENSOL</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="n">
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="n">
         <v>1702.8</v>
       </c>
-      <c r="H46" s="3" t="n">
+      <c r="I46" s="3" t="n">
         <v>1736.86</v>
       </c>
-      <c r="I46" s="3" t="n">
+      <c r="J46" s="3" t="n">
         <v>1689.18</v>
       </c>
-      <c r="J46" s="3" t="n">
+      <c r="K46" s="3" t="n">
         <v>1723.23</v>
       </c>
-      <c r="K46" s="3" t="n">
+      <c r="L46" s="3" t="n">
         <v>1736.86</v>
       </c>
-      <c r="L46" s="2" t="n">
+      <c r="M46" s="2" t="n">
         <v>153</v>
       </c>
-      <c r="M46" s="2" t="inlineStr">
+      <c r="N46" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N46" s="3" t="n">
+      <c r="O46" s="3" t="n">
         <v>5210.57</v>
       </c>
-      <c r="O46" s="4" t="n">
+      <c r="P46" s="4" t="n">
         <v>0.024991</v>
       </c>
-      <c r="P46" s="3" t="n">
+      <c r="Q46" s="3" t="n">
         <v>213704.93</v>
       </c>
     </row>
@@ -3190,54 +3406,59 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>AEGISLOG</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="n">
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="n">
         <v>1344</v>
       </c>
-      <c r="H47" s="3" t="n">
+      <c r="I47" s="3" t="n">
         <v>1370.88</v>
       </c>
-      <c r="I47" s="3" t="n">
+      <c r="J47" s="3" t="n">
         <v>1333.25</v>
       </c>
-      <c r="J47" s="3" t="n">
+      <c r="K47" s="3" t="n">
         <v>1360.13</v>
       </c>
-      <c r="K47" s="3" t="n">
+      <c r="L47" s="3" t="n">
         <v>1370.88</v>
       </c>
-      <c r="L47" s="2" t="n">
+      <c r="M47" s="2" t="n">
         <v>198</v>
       </c>
-      <c r="M47" s="2" t="inlineStr">
+      <c r="N47" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N47" s="3" t="n">
+      <c r="O47" s="3" t="n">
         <v>5322.24</v>
       </c>
-      <c r="O47" s="4" t="n">
+      <c r="P47" s="4" t="n">
         <v>0.024905</v>
       </c>
-      <c r="P47" s="3" t="n">
+      <c r="Q47" s="3" t="n">
         <v>219027.17</v>
       </c>
     </row>
@@ -3252,54 +3473,59 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>09:15 AM</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
           <t>09:25 AM</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>ANANDRATHI</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="n">
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="n">
         <v>2060</v>
       </c>
-      <c r="H48" s="3" t="n">
+      <c r="I48" s="3" t="n">
         <v>2084.72</v>
       </c>
-      <c r="I48" s="3" t="n">
+      <c r="J48" s="3" t="n">
         <v>2043.52</v>
       </c>
-      <c r="J48" s="3" t="n">
+      <c r="K48" s="3" t="n">
         <v>2084.72</v>
       </c>
-      <c r="K48" s="3" t="n">
+      <c r="L48" s="3" t="n">
         <v>2101.2</v>
       </c>
-      <c r="L48" s="2" t="n">
+      <c r="M48" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="M48" s="2" t="inlineStr">
+      <c r="N48" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N48" s="3" t="n">
+      <c r="O48" s="3" t="n">
         <v>3263.04</v>
       </c>
-      <c r="O48" s="4" t="n">
+      <c r="P48" s="4" t="n">
         <v>0.014898</v>
       </c>
-      <c r="P48" s="3" t="n">
+      <c r="Q48" s="3" t="n">
         <v>222290.21</v>
       </c>
     </row>
@@ -3314,54 +3540,59 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>ANTHEM</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="n">
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="n">
         <v>777.15</v>
       </c>
-      <c r="H49" s="3" t="n">
+      <c r="I49" s="3" t="n">
         <v>786.48</v>
       </c>
-      <c r="I49" s="3" t="n">
+      <c r="J49" s="3" t="n">
         <v>770.9299999999999</v>
       </c>
-      <c r="J49" s="3" t="n">
+      <c r="K49" s="3" t="n">
         <v>786.48</v>
       </c>
-      <c r="K49" s="3" t="n">
+      <c r="L49" s="3" t="n">
         <v>792.6900000000001</v>
       </c>
-      <c r="L49" s="2" t="n">
+      <c r="M49" s="2" t="n">
         <v>357</v>
       </c>
-      <c r="M49" s="2" t="inlineStr">
+      <c r="N49" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N49" s="3" t="n">
+      <c r="O49" s="3" t="n">
         <v>3329.31</v>
       </c>
-      <c r="O49" s="4" t="n">
+      <c r="P49" s="4" t="n">
         <v>0.014977</v>
       </c>
-      <c r="P49" s="3" t="n">
+      <c r="Q49" s="3" t="n">
         <v>225619.52</v>
       </c>
     </row>
@@ -3376,54 +3607,59 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>ACE</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G50" s="3" t="n">
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="n">
         <v>1010</v>
       </c>
-      <c r="H50" s="3" t="n">
+      <c r="I50" s="3" t="n">
         <v>1030.2</v>
       </c>
-      <c r="I50" s="3" t="n">
+      <c r="J50" s="3" t="n">
         <v>1001.92</v>
       </c>
-      <c r="J50" s="3" t="n">
+      <c r="K50" s="3" t="n">
         <v>1022.12</v>
       </c>
-      <c r="K50" s="3" t="n">
+      <c r="L50" s="3" t="n">
         <v>1030.2</v>
       </c>
-      <c r="L50" s="2" t="n">
+      <c r="M50" s="2" t="n">
         <v>279</v>
       </c>
-      <c r="M50" s="2" t="inlineStr">
+      <c r="N50" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N50" s="3" t="n">
+      <c r="O50" s="3" t="n">
         <v>5635.8</v>
       </c>
-      <c r="O50" s="4" t="n">
+      <c r="P50" s="4" t="n">
         <v>0.024979</v>
       </c>
-      <c r="P50" s="3" t="n">
+      <c r="Q50" s="3" t="n">
         <v>231255.32</v>
       </c>
     </row>
@@ -3438,54 +3674,59 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>AWL</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="n">
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="n">
         <v>189.05</v>
       </c>
-      <c r="H51" s="3" t="n">
+      <c r="I51" s="3" t="n">
         <v>191.32</v>
       </c>
-      <c r="I51" s="3" t="n">
+      <c r="J51" s="3" t="n">
         <v>187.54</v>
       </c>
-      <c r="J51" s="3" t="n">
+      <c r="K51" s="3" t="n">
         <v>191.32</v>
       </c>
-      <c r="K51" s="3" t="n">
+      <c r="L51" s="3" t="n">
         <v>192.83</v>
       </c>
-      <c r="L51" s="2" t="n">
+      <c r="M51" s="2" t="n">
         <v>1529</v>
       </c>
-      <c r="M51" s="2" t="inlineStr">
+      <c r="N51" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N51" s="3" t="n">
+      <c r="O51" s="3" t="n">
         <v>3468.69</v>
       </c>
-      <c r="O51" s="4" t="n">
+      <c r="P51" s="4" t="n">
         <v>0.014999</v>
       </c>
-      <c r="P51" s="3" t="n">
+      <c r="Q51" s="3" t="n">
         <v>234724.01</v>
       </c>
     </row>
@@ -3500,54 +3741,59 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>BERGEPAINT</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="n">
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="n">
         <v>492</v>
       </c>
-      <c r="H52" s="3" t="n">
+      <c r="I52" s="3" t="n">
         <v>497.9</v>
       </c>
-      <c r="I52" s="3" t="n">
+      <c r="J52" s="3" t="n">
         <v>488.06</v>
       </c>
-      <c r="J52" s="3" t="n">
+      <c r="K52" s="3" t="n">
         <v>497.9</v>
       </c>
-      <c r="K52" s="3" t="n">
+      <c r="L52" s="3" t="n">
         <v>501.84</v>
       </c>
-      <c r="L52" s="2" t="n">
+      <c r="M52" s="2" t="n">
         <v>596</v>
       </c>
-      <c r="M52" s="2" t="inlineStr">
+      <c r="N52" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N52" s="3" t="n">
+      <c r="O52" s="3" t="n">
         <v>3518.78</v>
       </c>
-      <c r="O52" s="4" t="n">
+      <c r="P52" s="4" t="n">
         <v>0.014991</v>
       </c>
-      <c r="P52" s="3" t="n">
+      <c r="Q52" s="3" t="n">
         <v>238242.8</v>
       </c>
     </row>
@@ -3562,54 +3808,59 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
           <t>AIIL</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="n">
-        <v>563.9</v>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
       </c>
       <c r="H53" s="6" t="n">
         <v>563.9</v>
       </c>
       <c r="I53" s="6" t="n">
+        <v>563.9</v>
+      </c>
+      <c r="J53" s="6" t="n">
         <v>559.39</v>
       </c>
-      <c r="J53" s="6" t="n">
+      <c r="K53" s="6" t="n">
         <v>570.67</v>
       </c>
-      <c r="K53" s="6" t="n">
+      <c r="L53" s="6" t="n">
         <v>575.1799999999999</v>
       </c>
-      <c r="L53" s="5" t="n">
+      <c r="M53" s="5" t="n">
         <v>528</v>
       </c>
-      <c r="M53" s="5" t="inlineStr">
+      <c r="N53" s="5" t="inlineStr">
         <is>
           <t>HIT_BE</t>
         </is>
       </c>
-      <c r="N53" s="6" t="n">
+      <c r="O53" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O53" s="7" t="n">
+      <c r="P53" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P53" s="6" t="n">
+      <c r="Q53" s="6" t="n">
         <v>238242.8</v>
       </c>
     </row>
@@ -3624,54 +3875,59 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>BAJAJ-AUTO</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="n">
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="n">
         <v>10615</v>
       </c>
-      <c r="H54" s="3" t="n">
+      <c r="I54" s="3" t="n">
         <v>10827.3</v>
       </c>
-      <c r="I54" s="3" t="n">
+      <c r="J54" s="3" t="n">
         <v>10530.08</v>
       </c>
-      <c r="J54" s="3" t="n">
+      <c r="K54" s="3" t="n">
         <v>10742.38</v>
       </c>
-      <c r="K54" s="3" t="n">
+      <c r="L54" s="3" t="n">
         <v>10827.3</v>
       </c>
-      <c r="L54" s="2" t="n">
+      <c r="M54" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="M54" s="2" t="inlineStr">
+      <c r="N54" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N54" s="3" t="n">
+      <c r="O54" s="3" t="n">
         <v>5944.4</v>
       </c>
-      <c r="O54" s="4" t="n">
+      <c r="P54" s="4" t="n">
         <v>0.024951</v>
       </c>
-      <c r="P54" s="3" t="n">
+      <c r="Q54" s="3" t="n">
         <v>244187.2</v>
       </c>
     </row>
@@ -3686,54 +3942,59 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>ANTHEM</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="n">
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="n">
         <v>742.2</v>
       </c>
-      <c r="H55" s="3" t="n">
+      <c r="I55" s="3" t="n">
         <v>757.04</v>
       </c>
-      <c r="I55" s="3" t="n">
+      <c r="J55" s="3" t="n">
         <v>736.26</v>
       </c>
-      <c r="J55" s="3" t="n">
+      <c r="K55" s="3" t="n">
         <v>751.11</v>
       </c>
-      <c r="K55" s="3" t="n">
+      <c r="L55" s="3" t="n">
         <v>757.04</v>
       </c>
-      <c r="L55" s="2" t="n">
+      <c r="M55" s="2" t="n">
         <v>411</v>
       </c>
-      <c r="M55" s="2" t="inlineStr">
+      <c r="N55" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N55" s="3" t="n">
+      <c r="O55" s="3" t="n">
         <v>6100.88</v>
       </c>
-      <c r="O55" s="4" t="n">
+      <c r="P55" s="4" t="n">
         <v>0.024984</v>
       </c>
-      <c r="P55" s="3" t="n">
+      <c r="Q55" s="3" t="n">
         <v>250288.08</v>
       </c>
     </row>
@@ -3748,54 +4009,59 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>BPCL</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="n">
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="n">
         <v>306</v>
       </c>
-      <c r="H56" s="3" t="n">
+      <c r="I56" s="3" t="n">
         <v>312.12</v>
       </c>
-      <c r="I56" s="3" t="n">
+      <c r="J56" s="3" t="n">
         <v>303.55</v>
       </c>
-      <c r="J56" s="3" t="n">
+      <c r="K56" s="3" t="n">
         <v>309.67</v>
       </c>
-      <c r="K56" s="3" t="n">
+      <c r="L56" s="3" t="n">
         <v>312.12</v>
       </c>
-      <c r="L56" s="2" t="n">
+      <c r="M56" s="2" t="n">
         <v>1022</v>
       </c>
-      <c r="M56" s="2" t="inlineStr">
+      <c r="N56" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N56" s="3" t="n">
+      <c r="O56" s="3" t="n">
         <v>6254.64</v>
       </c>
-      <c r="O56" s="4" t="n">
+      <c r="P56" s="4" t="n">
         <v>0.02499</v>
       </c>
-      <c r="P56" s="3" t="n">
+      <c r="Q56" s="3" t="n">
         <v>256542.72</v>
       </c>
     </row>
@@ -3810,54 +4076,59 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
           <t>APARINDS</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="n">
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="n">
         <v>13552</v>
       </c>
-      <c r="H57" s="3" t="n">
+      <c r="I57" s="3" t="n">
         <v>13714.62</v>
       </c>
-      <c r="I57" s="3" t="n">
+      <c r="J57" s="3" t="n">
         <v>13443.58</v>
       </c>
-      <c r="J57" s="3" t="n">
+      <c r="K57" s="3" t="n">
         <v>13714.62</v>
       </c>
-      <c r="K57" s="3" t="n">
+      <c r="L57" s="3" t="n">
         <v>13823.04</v>
       </c>
-      <c r="L57" s="2" t="n">
+      <c r="M57" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="M57" s="2" t="inlineStr">
+      <c r="N57" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N57" s="3" t="n">
+      <c r="O57" s="3" t="n">
         <v>3740.35</v>
       </c>
-      <c r="O57" s="4" t="n">
+      <c r="P57" s="4" t="n">
         <v>0.01458</v>
       </c>
-      <c r="P57" s="3" t="n">
+      <c r="Q57" s="3" t="n">
         <v>260283.07</v>
       </c>
     </row>
@@ -3872,54 +4143,59 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
           <t>AEGISLOG</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="n">
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="n">
         <v>1349</v>
       </c>
-      <c r="H58" s="3" t="n">
+      <c r="I58" s="3" t="n">
         <v>1365.19</v>
       </c>
-      <c r="I58" s="3" t="n">
+      <c r="J58" s="3" t="n">
         <v>1338.21</v>
       </c>
-      <c r="J58" s="3" t="n">
+      <c r="K58" s="3" t="n">
         <v>1365.19</v>
       </c>
-      <c r="K58" s="3" t="n">
+      <c r="L58" s="3" t="n">
         <v>1375.98</v>
       </c>
-      <c r="L58" s="2" t="n">
+      <c r="M58" s="2" t="n">
         <v>241</v>
       </c>
-      <c r="M58" s="2" t="inlineStr">
+      <c r="N58" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N58" s="3" t="n">
+      <c r="O58" s="3" t="n">
         <v>3901.31</v>
       </c>
-      <c r="O58" s="4" t="n">
+      <c r="P58" s="4" t="n">
         <v>0.014989</v>
       </c>
-      <c r="P58" s="3" t="n">
+      <c r="Q58" s="3" t="n">
         <v>264184.38</v>
       </c>
     </row>
@@ -3934,54 +4210,59 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
           <t>ABDL</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="n">
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="n">
         <v>584.85</v>
       </c>
-      <c r="H59" s="3" t="n">
+      <c r="I59" s="3" t="n">
         <v>596.55</v>
       </c>
-      <c r="I59" s="3" t="n">
+      <c r="J59" s="3" t="n">
         <v>580.17</v>
       </c>
-      <c r="J59" s="3" t="n">
+      <c r="K59" s="3" t="n">
         <v>591.87</v>
       </c>
-      <c r="K59" s="3" t="n">
+      <c r="L59" s="3" t="n">
         <v>596.55</v>
       </c>
-      <c r="L59" s="2" t="n">
+      <c r="M59" s="2" t="n">
         <v>564</v>
       </c>
-      <c r="M59" s="2" t="inlineStr">
+      <c r="N59" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N59" s="3" t="n">
+      <c r="O59" s="3" t="n">
         <v>6597.11</v>
       </c>
-      <c r="O59" s="4" t="n">
+      <c r="P59" s="4" t="n">
         <v>0.024972</v>
       </c>
-      <c r="P59" s="3" t="n">
+      <c r="Q59" s="3" t="n">
         <v>270781.49</v>
       </c>
     </row>
@@ -3996,54 +4277,59 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
           <t>ACE</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="n">
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="n">
         <v>975</v>
       </c>
-      <c r="H60" s="3" t="n">
+      <c r="I60" s="3" t="n">
         <v>986.7</v>
       </c>
-      <c r="I60" s="3" t="n">
+      <c r="J60" s="3" t="n">
         <v>967.2</v>
       </c>
-      <c r="J60" s="3" t="n">
+      <c r="K60" s="3" t="n">
         <v>986.7</v>
       </c>
-      <c r="K60" s="3" t="n">
+      <c r="L60" s="3" t="n">
         <v>994.5</v>
       </c>
-      <c r="L60" s="2" t="n">
+      <c r="M60" s="2" t="n">
         <v>347</v>
       </c>
-      <c r="M60" s="2" t="inlineStr">
+      <c r="N60" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N60" s="3" t="n">
+      <c r="O60" s="3" t="n">
         <v>4059.9</v>
       </c>
-      <c r="O60" s="4" t="n">
+      <c r="P60" s="4" t="n">
         <v>0.014993</v>
       </c>
-      <c r="P60" s="3" t="n">
+      <c r="Q60" s="3" t="n">
         <v>274841.39</v>
       </c>
     </row>
@@ -4058,54 +4344,59 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
           <t>DMART</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="n">
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="n">
         <v>3990</v>
       </c>
-      <c r="H61" s="3" t="n">
+      <c r="I61" s="3" t="n">
         <v>4037.88</v>
       </c>
-      <c r="I61" s="3" t="n">
+      <c r="J61" s="3" t="n">
         <v>3958.08</v>
       </c>
-      <c r="J61" s="3" t="n">
+      <c r="K61" s="3" t="n">
         <v>4037.88</v>
       </c>
-      <c r="K61" s="3" t="n">
+      <c r="L61" s="3" t="n">
         <v>4069.8</v>
       </c>
-      <c r="L61" s="2" t="n">
+      <c r="M61" s="2" t="n">
         <v>86</v>
       </c>
-      <c r="M61" s="2" t="inlineStr">
+      <c r="N61" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N61" s="3" t="n">
+      <c r="O61" s="3" t="n">
         <v>4117.68</v>
       </c>
-      <c r="O61" s="4" t="n">
+      <c r="P61" s="4" t="n">
         <v>0.014982</v>
       </c>
-      <c r="P61" s="3" t="n">
+      <c r="Q61" s="3" t="n">
         <v>278959.07</v>
       </c>
     </row>
@@ -4120,54 +4411,59 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
           <t>ACUTAAS</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="n">
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="n">
         <v>3273.5</v>
       </c>
-      <c r="H62" s="3" t="n">
+      <c r="I62" s="3" t="n">
         <v>3338.97</v>
       </c>
-      <c r="I62" s="3" t="n">
+      <c r="J62" s="3" t="n">
         <v>3247.31</v>
       </c>
-      <c r="J62" s="3" t="n">
+      <c r="K62" s="3" t="n">
         <v>3312.78</v>
       </c>
-      <c r="K62" s="3" t="n">
+      <c r="L62" s="3" t="n">
         <v>3338.97</v>
       </c>
-      <c r="L62" s="2" t="n">
+      <c r="M62" s="2" t="n">
         <v>106</v>
       </c>
-      <c r="M62" s="2" t="inlineStr">
+      <c r="N62" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N62" s="3" t="n">
+      <c r="O62" s="3" t="n">
         <v>6939.82</v>
       </c>
-      <c r="O62" s="4" t="n">
+      <c r="P62" s="4" t="n">
         <v>0.024878</v>
       </c>
-      <c r="P62" s="3" t="n">
+      <c r="Q62" s="3" t="n">
         <v>285898.89</v>
       </c>
     </row>
@@ -4182,54 +4478,59 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
+          <t>09:15 AM</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
           <t>09:25 AM</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>ABREL</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="n">
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="n">
         <v>1385.4</v>
       </c>
-      <c r="H63" s="3" t="n">
+      <c r="I63" s="3" t="n">
         <v>1402.02</v>
       </c>
-      <c r="I63" s="3" t="n">
+      <c r="J63" s="3" t="n">
         <v>1374.32</v>
       </c>
-      <c r="J63" s="3" t="n">
+      <c r="K63" s="3" t="n">
         <v>1402.02</v>
       </c>
-      <c r="K63" s="3" t="n">
+      <c r="L63" s="3" t="n">
         <v>1413.11</v>
       </c>
-      <c r="L63" s="2" t="n">
+      <c r="M63" s="2" t="n">
         <v>257</v>
       </c>
-      <c r="M63" s="2" t="inlineStr">
+      <c r="N63" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N63" s="3" t="n">
+      <c r="O63" s="3" t="n">
         <v>4272.57</v>
       </c>
-      <c r="O63" s="4" t="n">
+      <c r="P63" s="4" t="n">
         <v>0.014944</v>
       </c>
-      <c r="P63" s="3" t="n">
+      <c r="Q63" s="3" t="n">
         <v>290171.46</v>
       </c>
     </row>
@@ -4244,54 +4545,59 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
           <t>ACE</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="n">
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="n">
         <v>1049.6</v>
       </c>
-      <c r="H64" s="3" t="n">
+      <c r="I64" s="3" t="n">
         <v>1062.2</v>
       </c>
-      <c r="I64" s="3" t="n">
+      <c r="J64" s="3" t="n">
         <v>1041.2</v>
       </c>
-      <c r="J64" s="3" t="n">
+      <c r="K64" s="3" t="n">
         <v>1062.2</v>
       </c>
-      <c r="K64" s="3" t="n">
+      <c r="L64" s="3" t="n">
         <v>1070.59</v>
       </c>
-      <c r="L64" s="2" t="n">
+      <c r="M64" s="2" t="n">
         <v>345</v>
       </c>
-      <c r="M64" s="2" t="inlineStr">
+      <c r="N64" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N64" s="3" t="n">
+      <c r="O64" s="3" t="n">
         <v>4345.34</v>
       </c>
-      <c r="O64" s="4" t="n">
+      <c r="P64" s="4" t="n">
         <v>0.014975</v>
       </c>
-      <c r="P64" s="3" t="n">
+      <c r="Q64" s="3" t="n">
         <v>294516.81</v>
       </c>
     </row>
@@ -4306,54 +4612,59 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
           <t>AFFLE</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="n">
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="n">
         <v>1500</v>
       </c>
-      <c r="H65" s="3" t="n">
+      <c r="I65" s="3" t="n">
         <v>1530</v>
       </c>
-      <c r="I65" s="3" t="n">
+      <c r="J65" s="3" t="n">
         <v>1488</v>
       </c>
-      <c r="J65" s="3" t="n">
+      <c r="K65" s="3" t="n">
         <v>1518</v>
       </c>
-      <c r="K65" s="3" t="n">
+      <c r="L65" s="3" t="n">
         <v>1530</v>
       </c>
-      <c r="L65" s="2" t="n">
+      <c r="M65" s="2" t="n">
         <v>245</v>
       </c>
-      <c r="M65" s="2" t="inlineStr">
+      <c r="N65" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N65" s="3" t="n">
+      <c r="O65" s="3" t="n">
         <v>7350</v>
       </c>
-      <c r="O65" s="4" t="n">
+      <c r="P65" s="4" t="n">
         <v>0.024956</v>
       </c>
-      <c r="P65" s="3" t="n">
+      <c r="Q65" s="3" t="n">
         <v>301866.81</v>
       </c>
     </row>
@@ -4368,54 +4679,59 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
           <t>ACE</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="n">
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="n">
         <v>1058.5</v>
       </c>
-      <c r="H66" s="3" t="n">
+      <c r="I66" s="3" t="n">
         <v>1071.2</v>
       </c>
-      <c r="I66" s="3" t="n">
+      <c r="J66" s="3" t="n">
         <v>1050.03</v>
       </c>
-      <c r="J66" s="3" t="n">
+      <c r="K66" s="3" t="n">
         <v>1071.2</v>
       </c>
-      <c r="K66" s="3" t="n">
+      <c r="L66" s="3" t="n">
         <v>1079.67</v>
       </c>
-      <c r="L66" s="2" t="n">
+      <c r="M66" s="2" t="n">
         <v>356</v>
       </c>
-      <c r="M66" s="2" t="inlineStr">
+      <c r="N66" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N66" s="3" t="n">
+      <c r="O66" s="3" t="n">
         <v>4521.91</v>
       </c>
-      <c r="O66" s="4" t="n">
+      <c r="P66" s="4" t="n">
         <v>0.01498</v>
       </c>
-      <c r="P66" s="3" t="n">
+      <c r="Q66" s="3" t="n">
         <v>306388.72</v>
       </c>
     </row>
@@ -4430,54 +4746,59 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>09:15 AM</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
           <t>09:30 AM</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>ABDL</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="n">
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="n">
         <v>620.95</v>
       </c>
-      <c r="H67" s="3" t="n">
+      <c r="I67" s="3" t="n">
         <v>628.4</v>
       </c>
-      <c r="I67" s="3" t="n">
+      <c r="J67" s="3" t="n">
         <v>615.98</v>
       </c>
-      <c r="J67" s="3" t="n">
+      <c r="K67" s="3" t="n">
         <v>628.4</v>
       </c>
-      <c r="K67" s="3" t="n">
+      <c r="L67" s="3" t="n">
         <v>633.37</v>
       </c>
-      <c r="L67" s="2" t="n">
+      <c r="M67" s="2" t="n">
         <v>616</v>
       </c>
-      <c r="M67" s="2" t="inlineStr">
+      <c r="N67" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N67" s="3" t="n">
+      <c r="O67" s="3" t="n">
         <v>4590.06</v>
       </c>
-      <c r="O67" s="4" t="n">
+      <c r="P67" s="4" t="n">
         <v>0.014981</v>
       </c>
-      <c r="P67" s="3" t="n">
+      <c r="Q67" s="3" t="n">
         <v>310978.78</v>
       </c>
     </row>
@@ -4492,54 +4813,59 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
           <t>BALKRISIND</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="n">
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="n">
         <v>2023.4</v>
       </c>
-      <c r="H68" s="3" t="n">
+      <c r="I68" s="3" t="n">
         <v>2047.68</v>
       </c>
-      <c r="I68" s="3" t="n">
+      <c r="J68" s="3" t="n">
         <v>2007.21</v>
       </c>
-      <c r="J68" s="3" t="n">
+      <c r="K68" s="3" t="n">
         <v>2047.68</v>
       </c>
-      <c r="K68" s="3" t="n">
+      <c r="L68" s="3" t="n">
         <v>2063.87</v>
       </c>
-      <c r="L68" s="2" t="n">
+      <c r="M68" s="2" t="n">
         <v>192</v>
       </c>
-      <c r="M68" s="2" t="inlineStr">
+      <c r="N68" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N68" s="3" t="n">
+      <c r="O68" s="3" t="n">
         <v>4661.91</v>
       </c>
-      <c r="O68" s="4" t="n">
+      <c r="P68" s="4" t="n">
         <v>0.014991</v>
       </c>
-      <c r="P68" s="3" t="n">
+      <c r="Q68" s="3" t="n">
         <v>315640.69</v>
       </c>
     </row>
@@ -4554,54 +4880,59 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>AARTIIND</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="n">
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="n">
         <v>478.1</v>
       </c>
-      <c r="H69" s="3" t="n">
+      <c r="I69" s="3" t="n">
         <v>483.84</v>
       </c>
-      <c r="I69" s="3" t="n">
+      <c r="J69" s="3" t="n">
         <v>474.28</v>
       </c>
-      <c r="J69" s="3" t="n">
+      <c r="K69" s="3" t="n">
         <v>483.84</v>
       </c>
-      <c r="K69" s="3" t="n">
+      <c r="L69" s="3" t="n">
         <v>487.66</v>
       </c>
-      <c r="L69" s="2" t="n">
+      <c r="M69" s="2" t="n">
         <v>825</v>
       </c>
-      <c r="M69" s="2" t="inlineStr">
+      <c r="N69" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N69" s="3" t="n">
+      <c r="O69" s="3" t="n">
         <v>4733.19</v>
       </c>
-      <c r="O69" s="4" t="n">
+      <c r="P69" s="4" t="n">
         <v>0.014996</v>
       </c>
-      <c r="P69" s="3" t="n">
+      <c r="Q69" s="3" t="n">
         <v>320373.88</v>
       </c>
     </row>
@@ -4616,54 +4947,59 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>09:15 AM</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
           <t>09:35 AM</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>ALKEM</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="n">
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="n">
         <v>5689</v>
       </c>
-      <c r="H70" s="3" t="n">
+      <c r="I70" s="3" t="n">
         <v>5802.78</v>
       </c>
-      <c r="I70" s="3" t="n">
+      <c r="J70" s="3" t="n">
         <v>5643.49</v>
       </c>
-      <c r="J70" s="3" t="n">
+      <c r="K70" s="3" t="n">
         <v>5757.27</v>
       </c>
-      <c r="K70" s="3" t="n">
+      <c r="L70" s="3" t="n">
         <v>5802.78</v>
       </c>
-      <c r="L70" s="2" t="n">
+      <c r="M70" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="M70" s="2" t="inlineStr">
+      <c r="N70" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N70" s="3" t="n">
+      <c r="O70" s="3" t="n">
         <v>7964.6</v>
       </c>
-      <c r="O70" s="4" t="n">
+      <c r="P70" s="4" t="n">
         <v>0.02486</v>
       </c>
-      <c r="P70" s="3" t="n">
+      <c r="Q70" s="3" t="n">
         <v>328338.48</v>
       </c>
     </row>
@@ -4678,54 +5014,59 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>BALKRISIND</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="n">
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="n">
         <v>2230</v>
       </c>
-      <c r="H71" s="3" t="n">
+      <c r="I71" s="3" t="n">
         <v>2274.6</v>
       </c>
-      <c r="I71" s="3" t="n">
+      <c r="J71" s="3" t="n">
         <v>2212.16</v>
       </c>
-      <c r="J71" s="3" t="n">
+      <c r="K71" s="3" t="n">
         <v>2256.76</v>
       </c>
-      <c r="K71" s="3" t="n">
+      <c r="L71" s="3" t="n">
         <v>2274.6</v>
       </c>
-      <c r="L71" s="2" t="n">
+      <c r="M71" s="2" t="n">
         <v>184</v>
       </c>
-      <c r="M71" s="2" t="inlineStr">
+      <c r="N71" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N71" s="3" t="n">
+      <c r="O71" s="3" t="n">
         <v>8206.4</v>
       </c>
-      <c r="O71" s="4" t="n">
+      <c r="P71" s="4" t="n">
         <v>0.024994</v>
       </c>
-      <c r="P71" s="3" t="n">
+      <c r="Q71" s="3" t="n">
         <v>336544.88</v>
       </c>
     </row>
@@ -4740,54 +5081,59 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>AJANTPHARM</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="n">
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="n">
         <v>3355.1</v>
       </c>
-      <c r="H72" s="3" t="n">
+      <c r="I72" s="3" t="n">
         <v>3422.2</v>
       </c>
-      <c r="I72" s="3" t="n">
+      <c r="J72" s="3" t="n">
         <v>3328.26</v>
       </c>
-      <c r="J72" s="3" t="n">
+      <c r="K72" s="3" t="n">
         <v>3395.36</v>
       </c>
-      <c r="K72" s="3" t="n">
+      <c r="L72" s="3" t="n">
         <v>3422.2</v>
       </c>
-      <c r="L72" s="2" t="n">
+      <c r="M72" s="2" t="n">
         <v>125</v>
       </c>
-      <c r="M72" s="2" t="inlineStr">
+      <c r="N72" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N72" s="3" t="n">
+      <c r="O72" s="3" t="n">
         <v>8387.75</v>
       </c>
-      <c r="O72" s="4" t="n">
+      <c r="P72" s="4" t="n">
         <v>0.024923</v>
       </c>
-      <c r="P72" s="3" t="n">
+      <c r="Q72" s="3" t="n">
         <v>344932.63</v>
       </c>
     </row>
@@ -4802,54 +5148,59 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>BALKRISIND</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="n">
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="n">
         <v>2344.1</v>
       </c>
-      <c r="H73" s="3" t="n">
+      <c r="I73" s="3" t="n">
         <v>2372.23</v>
       </c>
-      <c r="I73" s="3" t="n">
+      <c r="J73" s="3" t="n">
         <v>2325.35</v>
       </c>
-      <c r="J73" s="3" t="n">
+      <c r="K73" s="3" t="n">
         <v>2372.23</v>
       </c>
-      <c r="K73" s="3" t="n">
+      <c r="L73" s="3" t="n">
         <v>2390.98</v>
       </c>
-      <c r="L73" s="2" t="n">
+      <c r="M73" s="2" t="n">
         <v>183</v>
       </c>
-      <c r="M73" s="2" t="inlineStr">
+      <c r="N73" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N73" s="3" t="n">
+      <c r="O73" s="3" t="n">
         <v>5147.64</v>
       </c>
-      <c r="O73" s="4" t="n">
+      <c r="P73" s="4" t="n">
         <v>0.014924</v>
       </c>
-      <c r="P73" s="3" t="n">
+      <c r="Q73" s="3" t="n">
         <v>350080.28</v>
       </c>
     </row>
@@ -4864,54 +5215,59 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>CPPLUS</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G74" s="3" t="n">
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="n">
         <v>3285.9</v>
       </c>
-      <c r="H74" s="3" t="n">
+      <c r="I74" s="3" t="n">
         <v>3325.33</v>
       </c>
-      <c r="I74" s="3" t="n">
+      <c r="J74" s="3" t="n">
         <v>3259.61</v>
       </c>
-      <c r="J74" s="3" t="n">
+      <c r="K74" s="3" t="n">
         <v>3325.33</v>
       </c>
-      <c r="K74" s="3" t="n">
+      <c r="L74" s="3" t="n">
         <v>3351.62</v>
       </c>
-      <c r="L74" s="2" t="n">
+      <c r="M74" s="2" t="n">
         <v>133</v>
       </c>
-      <c r="M74" s="2" t="inlineStr">
+      <c r="N74" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N74" s="3" t="n">
+      <c r="O74" s="3" t="n">
         <v>5244.3</v>
       </c>
-      <c r="O74" s="4" t="n">
+      <c r="P74" s="4" t="n">
         <v>0.01498</v>
       </c>
-      <c r="P74" s="3" t="n">
+      <c r="Q74" s="3" t="n">
         <v>355324.57</v>
       </c>
     </row>
@@ -4926,54 +5282,59 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>09:15 AM</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
           <t>09:30 AM</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>ASHOKLEY</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G75" s="3" t="n">
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="n">
         <v>159.97</v>
       </c>
-      <c r="H75" s="3" t="n">
+      <c r="I75" s="3" t="n">
         <v>161.89</v>
       </c>
-      <c r="I75" s="3" t="n">
+      <c r="J75" s="3" t="n">
         <v>158.69</v>
       </c>
-      <c r="J75" s="3" t="n">
+      <c r="K75" s="3" t="n">
         <v>161.89</v>
       </c>
-      <c r="K75" s="3" t="n">
+      <c r="L75" s="3" t="n">
         <v>163.17</v>
       </c>
-      <c r="L75" s="2" t="n">
+      <c r="M75" s="2" t="n">
         <v>2776</v>
       </c>
-      <c r="M75" s="2" t="inlineStr">
+      <c r="N75" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N75" s="3" t="n">
+      <c r="O75" s="3" t="n">
         <v>5328.92</v>
       </c>
-      <c r="O75" s="4" t="n">
+      <c r="P75" s="4" t="n">
         <v>0.014997</v>
       </c>
-      <c r="P75" s="3" t="n">
+      <c r="Q75" s="3" t="n">
         <v>360653.49</v>
       </c>
     </row>
@@ -4988,54 +5349,59 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>AAVAS</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G76" s="3" t="n">
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="n">
         <v>1359.8</v>
       </c>
-      <c r="H76" s="3" t="n">
+      <c r="I76" s="3" t="n">
         <v>1387</v>
       </c>
-      <c r="I76" s="3" t="n">
+      <c r="J76" s="3" t="n">
         <v>1348.92</v>
       </c>
-      <c r="J76" s="3" t="n">
+      <c r="K76" s="3" t="n">
         <v>1376.12</v>
       </c>
-      <c r="K76" s="3" t="n">
+      <c r="L76" s="3" t="n">
         <v>1387</v>
       </c>
-      <c r="L76" s="2" t="n">
+      <c r="M76" s="2" t="n">
         <v>331</v>
       </c>
-      <c r="M76" s="2" t="inlineStr">
+      <c r="N76" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N76" s="3" t="n">
+      <c r="O76" s="3" t="n">
         <v>9001.879999999999</v>
       </c>
-      <c r="O76" s="4" t="n">
+      <c r="P76" s="4" t="n">
         <v>0.02496</v>
       </c>
-      <c r="P76" s="3" t="n">
+      <c r="Q76" s="3" t="n">
         <v>369655.37</v>
       </c>
     </row>
@@ -5050,54 +5416,59 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>ABCAPITAL</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G77" s="3" t="n">
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="n">
         <v>410.9</v>
       </c>
-      <c r="H77" s="3" t="n">
+      <c r="I77" s="3" t="n">
         <v>419.12</v>
       </c>
-      <c r="I77" s="3" t="n">
+      <c r="J77" s="3" t="n">
         <v>407.61</v>
       </c>
-      <c r="J77" s="3" t="n">
+      <c r="K77" s="3" t="n">
         <v>415.83</v>
       </c>
-      <c r="K77" s="3" t="n">
+      <c r="L77" s="3" t="n">
         <v>419.12</v>
       </c>
-      <c r="L77" s="2" t="n">
+      <c r="M77" s="2" t="n">
         <v>1124</v>
       </c>
-      <c r="M77" s="2" t="inlineStr">
+      <c r="N77" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N77" s="3" t="n">
+      <c r="O77" s="3" t="n">
         <v>9237.030000000001</v>
       </c>
-      <c r="O77" s="4" t="n">
+      <c r="P77" s="4" t="n">
         <v>0.024988</v>
       </c>
-      <c r="P77" s="3" t="n">
+      <c r="Q77" s="3" t="n">
         <v>378892.4</v>
       </c>
     </row>
@@ -5112,54 +5483,59 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>BALRAMCHIN</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G78" s="3" t="n">
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="n">
         <v>597</v>
       </c>
-      <c r="H78" s="3" t="n">
+      <c r="I78" s="3" t="n">
         <v>608.9400000000001</v>
       </c>
-      <c r="I78" s="3" t="n">
+      <c r="J78" s="3" t="n">
         <v>592.22</v>
       </c>
-      <c r="J78" s="3" t="n">
+      <c r="K78" s="3" t="n">
         <v>604.16</v>
       </c>
-      <c r="K78" s="3" t="n">
+      <c r="L78" s="3" t="n">
         <v>608.9400000000001</v>
       </c>
-      <c r="L78" s="2" t="n">
+      <c r="M78" s="2" t="n">
         <v>793</v>
       </c>
-      <c r="M78" s="2" t="inlineStr">
+      <c r="N78" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N78" s="3" t="n">
+      <c r="O78" s="3" t="n">
         <v>9468.42</v>
       </c>
-      <c r="O78" s="4" t="n">
+      <c r="P78" s="4" t="n">
         <v>0.02499</v>
       </c>
-      <c r="P78" s="3" t="n">
+      <c r="Q78" s="3" t="n">
         <v>388360.82</v>
       </c>
     </row>
@@ -5174,54 +5550,59 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t>ATHERENERG</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G79" s="3" t="n">
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="n">
         <v>1349.4</v>
       </c>
-      <c r="H79" s="3" t="n">
+      <c r="I79" s="3" t="n">
         <v>1376.39</v>
       </c>
-      <c r="I79" s="3" t="n">
+      <c r="J79" s="3" t="n">
         <v>1338.6</v>
       </c>
-      <c r="J79" s="3" t="n">
+      <c r="K79" s="3" t="n">
         <v>1365.59</v>
       </c>
-      <c r="K79" s="3" t="n">
+      <c r="L79" s="3" t="n">
         <v>1376.39</v>
       </c>
-      <c r="L79" s="2" t="n">
+      <c r="M79" s="2" t="n">
         <v>359</v>
       </c>
-      <c r="M79" s="2" t="inlineStr">
+      <c r="N79" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N79" s="3" t="n">
+      <c r="O79" s="3" t="n">
         <v>9688.690000000001</v>
       </c>
-      <c r="O79" s="4" t="n">
+      <c r="P79" s="4" t="n">
         <v>0.024948</v>
       </c>
-      <c r="P79" s="3" t="n">
+      <c r="Q79" s="3" t="n">
         <v>398049.52</v>
       </c>
     </row>
@@ -5236,54 +5617,59 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
           <t>ACUTAAS</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G80" s="3" t="n">
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="n">
         <v>3075.1</v>
       </c>
-      <c r="H80" s="3" t="n">
+      <c r="I80" s="3" t="n">
         <v>3136.6</v>
       </c>
-      <c r="I80" s="3" t="n">
+      <c r="J80" s="3" t="n">
         <v>3050.5</v>
       </c>
-      <c r="J80" s="3" t="n">
+      <c r="K80" s="3" t="n">
         <v>3112</v>
       </c>
-      <c r="K80" s="3" t="n">
+      <c r="L80" s="3" t="n">
         <v>3136.6</v>
       </c>
-      <c r="L80" s="2" t="n">
+      <c r="M80" s="2" t="n">
         <v>161</v>
       </c>
-      <c r="M80" s="2" t="inlineStr">
+      <c r="N80" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N80" s="3" t="n">
+      <c r="O80" s="3" t="n">
         <v>9901.82</v>
       </c>
-      <c r="O80" s="4" t="n">
+      <c r="P80" s="4" t="n">
         <v>0.024876</v>
       </c>
-      <c r="P80" s="3" t="n">
+      <c r="Q80" s="3" t="n">
         <v>407951.34</v>
       </c>
     </row>
@@ -5298,54 +5684,59 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
           <t>APARINDS</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="n">
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="n">
         <v>14826</v>
       </c>
-      <c r="H81" s="3" t="n">
+      <c r="I81" s="3" t="n">
         <v>15003.91</v>
       </c>
-      <c r="I81" s="3" t="n">
+      <c r="J81" s="3" t="n">
         <v>14707.39</v>
       </c>
-      <c r="J81" s="3" t="n">
+      <c r="K81" s="3" t="n">
         <v>15003.91</v>
       </c>
-      <c r="K81" s="3" t="n">
+      <c r="L81" s="3" t="n">
         <v>15122.52</v>
       </c>
-      <c r="L81" s="2" t="n">
+      <c r="M81" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="M81" s="2" t="inlineStr">
+      <c r="N81" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N81" s="3" t="n">
+      <c r="O81" s="3" t="n">
         <v>6049.01</v>
       </c>
-      <c r="O81" s="4" t="n">
+      <c r="P81" s="4" t="n">
         <v>0.014828</v>
       </c>
-      <c r="P81" s="3" t="n">
+      <c r="Q81" s="3" t="n">
         <v>414000.35</v>
       </c>
     </row>
@@ -5360,54 +5751,59 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
           <t>BALKRISIND</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G82" s="3" t="n">
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="n">
         <v>2469.8</v>
       </c>
-      <c r="H82" s="3" t="n">
+      <c r="I82" s="3" t="n">
         <v>2519.2</v>
       </c>
-      <c r="I82" s="3" t="n">
+      <c r="J82" s="3" t="n">
         <v>2450.04</v>
       </c>
-      <c r="J82" s="3" t="n">
+      <c r="K82" s="3" t="n">
         <v>2499.44</v>
       </c>
-      <c r="K82" s="3" t="n">
+      <c r="L82" s="3" t="n">
         <v>2519.2</v>
       </c>
-      <c r="L82" s="2" t="n">
+      <c r="M82" s="2" t="n">
         <v>209</v>
       </c>
-      <c r="M82" s="2" t="inlineStr">
+      <c r="N82" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N82" s="3" t="n">
+      <c r="O82" s="3" t="n">
         <v>10323.76</v>
       </c>
-      <c r="O82" s="4" t="n">
+      <c r="P82" s="4" t="n">
         <v>0.024937</v>
       </c>
-      <c r="P82" s="3" t="n">
+      <c r="Q82" s="3" t="n">
         <v>424324.11</v>
       </c>
     </row>
@@ -5422,54 +5818,59 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
           <t>ARE&amp;M</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G83" s="3" t="n">
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="n">
         <v>928</v>
       </c>
-      <c r="H83" s="3" t="n">
+      <c r="I83" s="3" t="n">
         <v>939.14</v>
       </c>
-      <c r="I83" s="3" t="n">
+      <c r="J83" s="3" t="n">
         <v>920.58</v>
       </c>
-      <c r="J83" s="3" t="n">
+      <c r="K83" s="3" t="n">
         <v>939.14</v>
       </c>
-      <c r="K83" s="3" t="n">
+      <c r="L83" s="3" t="n">
         <v>946.5599999999999</v>
       </c>
-      <c r="L83" s="2" t="n">
+      <c r="M83" s="2" t="n">
         <v>571</v>
       </c>
-      <c r="M83" s="2" t="inlineStr">
+      <c r="N83" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N83" s="3" t="n">
+      <c r="O83" s="3" t="n">
         <v>6358.66</v>
       </c>
-      <c r="O83" s="4" t="n">
+      <c r="P83" s="4" t="n">
         <v>0.014985</v>
       </c>
-      <c r="P83" s="3" t="n">
+      <c r="Q83" s="3" t="n">
         <v>430682.77</v>
       </c>
     </row>
@@ -5484,54 +5885,59 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
           <t>BLS</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G84" s="3" t="n">
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="n">
         <v>249.28</v>
       </c>
-      <c r="H84" s="3" t="n">
+      <c r="I84" s="3" t="n">
         <v>252.27</v>
       </c>
-      <c r="I84" s="3" t="n">
+      <c r="J84" s="3" t="n">
         <v>247.29</v>
       </c>
-      <c r="J84" s="3" t="n">
+      <c r="K84" s="3" t="n">
         <v>252.27</v>
       </c>
-      <c r="K84" s="3" t="n">
+      <c r="L84" s="3" t="n">
         <v>254.27</v>
       </c>
-      <c r="L84" s="2" t="n">
+      <c r="M84" s="2" t="n">
         <v>2159</v>
       </c>
-      <c r="M84" s="2" t="inlineStr">
+      <c r="N84" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N84" s="3" t="n">
+      <c r="O84" s="3" t="n">
         <v>6458.35</v>
       </c>
-      <c r="O84" s="4" t="n">
+      <c r="P84" s="4" t="n">
         <v>0.014996</v>
       </c>
-      <c r="P84" s="3" t="n">
+      <c r="Q84" s="3" t="n">
         <v>437141.11</v>
       </c>
     </row>
@@ -5546,54 +5952,59 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
           <t>AEGISVOPAK</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G85" s="3" t="n">
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="n">
         <v>279</v>
       </c>
-      <c r="H85" s="3" t="n">
+      <c r="I85" s="3" t="n">
         <v>284.58</v>
       </c>
-      <c r="I85" s="3" t="n">
+      <c r="J85" s="3" t="n">
         <v>276.77</v>
       </c>
-      <c r="J85" s="3" t="n">
+      <c r="K85" s="3" t="n">
         <v>282.35</v>
       </c>
-      <c r="K85" s="3" t="n">
+      <c r="L85" s="3" t="n">
         <v>284.58</v>
       </c>
-      <c r="L85" s="2" t="n">
+      <c r="M85" s="2" t="n">
         <v>1958</v>
       </c>
-      <c r="M85" s="2" t="inlineStr">
+      <c r="N85" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N85" s="3" t="n">
+      <c r="O85" s="3" t="n">
         <v>10925.64</v>
       </c>
-      <c r="O85" s="4" t="n">
+      <c r="P85" s="4" t="n">
         <v>0.024993</v>
       </c>
-      <c r="P85" s="3" t="n">
+      <c r="Q85" s="3" t="n">
         <v>448066.75</v>
       </c>
     </row>
@@ -5608,54 +6019,59 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
           <t>ASTERDM</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G86" s="3" t="n">
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="n">
         <v>811.25</v>
       </c>
-      <c r="H86" s="3" t="n">
+      <c r="I86" s="3" t="n">
         <v>820.98</v>
       </c>
-      <c r="I86" s="3" t="n">
+      <c r="J86" s="3" t="n">
         <v>804.76</v>
       </c>
-      <c r="J86" s="3" t="n">
+      <c r="K86" s="3" t="n">
         <v>820.98</v>
       </c>
-      <c r="K86" s="3" t="n">
+      <c r="L86" s="3" t="n">
         <v>827.48</v>
       </c>
-      <c r="L86" s="2" t="n">
+      <c r="M86" s="2" t="n">
         <v>690</v>
       </c>
-      <c r="M86" s="2" t="inlineStr">
+      <c r="N86" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N86" s="3" t="n">
+      <c r="O86" s="3" t="n">
         <v>6717.15</v>
       </c>
-      <c r="O86" s="4" t="n">
+      <c r="P86" s="4" t="n">
         <v>0.014991</v>
       </c>
-      <c r="P86" s="3" t="n">
+      <c r="Q86" s="3" t="n">
         <v>454783.9</v>
       </c>
     </row>
@@ -5670,54 +6086,59 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
           <t>AWL</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G87" s="3" t="n">
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="n">
         <v>193.05</v>
       </c>
-      <c r="H87" s="3" t="n">
+      <c r="I87" s="3" t="n">
         <v>195.37</v>
       </c>
-      <c r="I87" s="3" t="n">
+      <c r="J87" s="3" t="n">
         <v>191.51</v>
       </c>
-      <c r="J87" s="3" t="n">
+      <c r="K87" s="3" t="n">
         <v>195.37</v>
       </c>
-      <c r="K87" s="3" t="n">
+      <c r="L87" s="3" t="n">
         <v>196.91</v>
       </c>
-      <c r="L87" s="2" t="n">
+      <c r="M87" s="2" t="n">
         <v>2944</v>
       </c>
-      <c r="M87" s="2" t="inlineStr">
+      <c r="N87" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N87" s="3" t="n">
+      <c r="O87" s="3" t="n">
         <v>6820.07</v>
       </c>
-      <c r="O87" s="4" t="n">
+      <c r="P87" s="4" t="n">
         <v>0.014996</v>
       </c>
-      <c r="P87" s="3" t="n">
+      <c r="Q87" s="3" t="n">
         <v>461603.97</v>
       </c>
     </row>
@@ -5732,54 +6153,59 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
           <t>ATHERENERG</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G88" s="3" t="n">
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="n">
         <v>1446</v>
       </c>
-      <c r="H88" s="3" t="n">
+      <c r="I88" s="3" t="n">
         <v>1474.92</v>
       </c>
-      <c r="I88" s="3" t="n">
+      <c r="J88" s="3" t="n">
         <v>1434.43</v>
       </c>
-      <c r="J88" s="3" t="n">
+      <c r="K88" s="3" t="n">
         <v>1463.35</v>
       </c>
-      <c r="K88" s="3" t="n">
+      <c r="L88" s="3" t="n">
         <v>1474.92</v>
       </c>
-      <c r="L88" s="2" t="n">
+      <c r="M88" s="2" t="n">
         <v>399</v>
       </c>
-      <c r="M88" s="2" t="inlineStr">
+      <c r="N88" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N88" s="3" t="n">
+      <c r="O88" s="3" t="n">
         <v>11539.08</v>
       </c>
-      <c r="O88" s="4" t="n">
+      <c r="P88" s="4" t="n">
         <v>0.024998</v>
       </c>
-      <c r="P88" s="3" t="n">
+      <c r="Q88" s="3" t="n">
         <v>473143.05</v>
       </c>
     </row>
@@ -5794,54 +6220,59 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
           <t>BALKRISIND</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G89" s="3" t="n">
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="n">
         <v>2441.9</v>
       </c>
-      <c r="H89" s="3" t="n">
+      <c r="I89" s="3" t="n">
         <v>2471.2</v>
       </c>
-      <c r="I89" s="3" t="n">
+      <c r="J89" s="3" t="n">
         <v>2422.36</v>
       </c>
-      <c r="J89" s="3" t="n">
+      <c r="K89" s="3" t="n">
         <v>2471.2</v>
       </c>
-      <c r="K89" s="3" t="n">
+      <c r="L89" s="3" t="n">
         <v>2490.74</v>
       </c>
-      <c r="L89" s="2" t="n">
+      <c r="M89" s="2" t="n">
         <v>242</v>
       </c>
-      <c r="M89" s="2" t="inlineStr">
+      <c r="N89" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N89" s="3" t="n">
+      <c r="O89" s="3" t="n">
         <v>7091.28</v>
       </c>
-      <c r="O89" s="4" t="n">
+      <c r="P89" s="4" t="n">
         <v>0.014988</v>
       </c>
-      <c r="P89" s="3" t="n">
+      <c r="Q89" s="3" t="n">
         <v>480234.33</v>
       </c>
     </row>
@@ -5856,54 +6287,59 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
           <t>ACMESOLAR</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G90" s="3" t="n">
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="n">
         <v>372</v>
       </c>
-      <c r="H90" s="3" t="n">
+      <c r="I90" s="3" t="n">
         <v>376.46</v>
       </c>
-      <c r="I90" s="3" t="n">
+      <c r="J90" s="3" t="n">
         <v>369.02</v>
       </c>
-      <c r="J90" s="3" t="n">
+      <c r="K90" s="3" t="n">
         <v>376.46</v>
       </c>
-      <c r="K90" s="3" t="n">
+      <c r="L90" s="3" t="n">
         <v>379.44</v>
       </c>
-      <c r="L90" s="2" t="n">
+      <c r="M90" s="2" t="n">
         <v>1613</v>
       </c>
-      <c r="M90" s="2" t="inlineStr">
+      <c r="N90" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N90" s="3" t="n">
+      <c r="O90" s="3" t="n">
         <v>7200.43</v>
       </c>
-      <c r="O90" s="4" t="n">
+      <c r="P90" s="4" t="n">
         <v>0.014994</v>
       </c>
-      <c r="P90" s="3" t="n">
+      <c r="Q90" s="3" t="n">
         <v>487434.76</v>
       </c>
     </row>
@@ -5918,54 +6354,59 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
+          <t>09:15 AM</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
           <t>09:25 AM</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>BEML</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G91" s="3" t="n">
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="n">
         <v>1787.8</v>
       </c>
-      <c r="H91" s="3" t="n">
+      <c r="I91" s="3" t="n">
         <v>1823.56</v>
       </c>
-      <c r="I91" s="3" t="n">
+      <c r="J91" s="3" t="n">
         <v>1773.5</v>
       </c>
-      <c r="J91" s="3" t="n">
+      <c r="K91" s="3" t="n">
         <v>1809.25</v>
       </c>
-      <c r="K91" s="3" t="n">
+      <c r="L91" s="3" t="n">
         <v>1823.56</v>
       </c>
-      <c r="L91" s="2" t="n">
+      <c r="M91" s="2" t="n">
         <v>340</v>
       </c>
-      <c r="M91" s="2" t="inlineStr">
+      <c r="N91" s="2" t="inlineStr">
         <is>
           <t>HIT_T2</t>
         </is>
       </c>
-      <c r="N91" s="3" t="n">
+      <c r="O91" s="3" t="n">
         <v>12157.04</v>
       </c>
-      <c r="O91" s="4" t="n">
+      <c r="P91" s="4" t="n">
         <v>0.024941</v>
       </c>
-      <c r="P91" s="3" t="n">
+      <c r="Q91" s="3" t="n">
         <v>499591.8</v>
       </c>
     </row>
@@ -5980,54 +6421,59 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
           <t>ASTERDM</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G92" s="3" t="n">
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="n">
         <v>868</v>
       </c>
-      <c r="H92" s="3" t="n">
+      <c r="I92" s="3" t="n">
         <v>878.42</v>
       </c>
-      <c r="I92" s="3" t="n">
+      <c r="J92" s="3" t="n">
         <v>861.0599999999999</v>
       </c>
-      <c r="J92" s="3" t="n">
+      <c r="K92" s="3" t="n">
         <v>878.42</v>
       </c>
-      <c r="K92" s="3" t="n">
+      <c r="L92" s="3" t="n">
         <v>885.36</v>
       </c>
-      <c r="L92" s="2" t="n">
+      <c r="M92" s="2" t="n">
         <v>719</v>
       </c>
-      <c r="M92" s="2" t="inlineStr">
+      <c r="N92" s="2" t="inlineStr">
         <is>
           <t>HIT_T1</t>
         </is>
       </c>
-      <c r="N92" s="3" t="n">
+      <c r="O92" s="3" t="n">
         <v>7489.1</v>
       </c>
-      <c r="O92" s="4" t="n">
+      <c r="P92" s="4" t="n">
         <v>0.01499</v>
       </c>
-      <c r="P92" s="3" t="n">
+      <c r="Q92" s="3" t="n">
         <v>507080.91</v>
       </c>
     </row>
@@ -6042,54 +6488,59 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>09:15 AM</t>
+          <t>09:05 AM</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>09:20 AM</t>
+          <t>09:15 AM</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
+          <t>09:20 AM</t>
+        </is>
+      </c>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
           <t>APARINDS</t>
         </is>
       </c>
-      <c r="F93" s="8" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G93" s="9" t="n">
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="H93" s="9" t="n">
         <v>16675</v>
-      </c>
-      <c r="H93" s="9" t="n">
-        <v>16541.6</v>
       </c>
       <c r="I93" s="9" t="n">
         <v>16541.6</v>
       </c>
       <c r="J93" s="9" t="n">
+        <v>16541.6</v>
+      </c>
+      <c r="K93" s="9" t="n">
         <v>16875.1</v>
       </c>
-      <c r="K93" s="9" t="n">
+      <c r="L93" s="9" t="n">
         <v>17008.5</v>
       </c>
-      <c r="L93" s="8" t="n">
+      <c r="M93" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="M93" s="8" t="inlineStr">
+      <c r="N93" s="8" t="inlineStr">
         <is>
           <t>HIT_SL</t>
         </is>
       </c>
-      <c r="N93" s="9" t="n">
+      <c r="O93" s="9" t="n">
         <v>-5069.2</v>
       </c>
-      <c r="O93" s="10" t="n">
+      <c r="P93" s="10" t="n">
         <v>-0.009997000000000001</v>
       </c>
-      <c r="P93" s="9" t="n">
+      <c r="Q93" s="9" t="n">
         <v>502011.71</v>
       </c>
     </row>
